--- a/Excel/3_3_Enteric_Dairy_WIP_v04.xlsx
+++ b/Excel/3_3_Enteric_Dairy_WIP_v04.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5762A2E4-E3CE-46B1-A3A2-18E5F34B8A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F10804B-592F-4186-B3D2-B6571CC20613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="990" yWindow="195" windowWidth="37170" windowHeight="19920" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="36060" windowHeight="19710" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -3753,32 +3753,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFB2D498"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -4664,6 +4638,32 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFB2D498"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9382,7 +9382,7 @@
   </autoFilter>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F2B173A3-CADE-4DCA-988D-39EE2392D8DB}" name="MMS"/>
-    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="43" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{67006656-167A-4452-9820-88D798B88ADD}" name="Symbol and MMS" dataDxfId="80" dataCellStyle="Content normal"/>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9400,13 +9400,13 @@
     <tableColumn id="1" xr3:uid="{8ACEF380-8A1A-411E-A23A-665A769E20C7}" name="MMS m">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1898B440-928B-49CE-BE96-215FD9903B4D}" name="EFm" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1898B440-928B-49CE-BE96-215FD9903B4D}" name="EFm" dataDxfId="55" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E38469E4-0572-4872-BE43-36C7BBE75007}" name="FracGASMm" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{E38469E4-0572-4872-BE43-36C7BBE75007}" name="FracGASMm" dataDxfId="54" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2136786A-A3D3-4E62-B5A7-46AAC51855AD}" name="NIR reference" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{2136786A-A3D3-4E62-B5A7-46AAC51855AD}" name="NIR reference" dataDxfId="53" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_NitrousOxideEFsAndFracGASM_Data(), Table_SourceData_Dairy_EFmFracGASM[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9424,7 +9424,7 @@
     <tableColumn id="1" xr3:uid="{34872B36-E9B0-443E-A8EC-EC35C2572085}" name="Animal class j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MethaneProductionPreWeanedCalves_Data(), Table_SourceData_Dairy_MPWENTERIC[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5BF46DC3-A57C-4E83-B386-D48BB1DB64E1}" name="MPW ENTERIC" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{5BF46DC3-A57C-4E83-B386-D48BB1DB64E1}" name="MPW ENTERIC" dataDxfId="52" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MethaneProductionPreWeanedCalves_Data(), Table_SourceData_Dairy_MPWENTERIC[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9442,7 +9442,7 @@
     <tableColumn id="1" xr3:uid="{B2383F7B-29D1-4559-9E34-4E2C127CFB5C}" name="Animal class j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_IncreasedMetabolicRateMilk_Data(), Table_SourceData_Dairy_MRj[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D1C6DB76-173B-4192-987A-A32F6D0D0E1A}" name="MRj" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D1C6DB76-173B-4192-987A-A32F6D0D0E1A}" name="MRj" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_IncreasedMetabolicRateMilk_Data(), Table_SourceData_Dairy_MRj[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9462,13 +9462,13 @@
     <tableColumn id="1" xr3:uid="{A4A196FD-DBDB-46C0-83CE-7C77F2C477B3}" name="Area">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{53A25CAD-C5FE-4619-A71E-7D4EE15E4A88}" name="Pasture" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{53A25CAD-C5FE-4619-A71E-7D4EE15E4A88}" name="Pasture" dataDxfId="50" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9DFD752F-089A-45B1-A1B3-329B65BC5650}" name="Milking shed" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9DFD752F-089A-45B1-A1B3-329B65BC5650}" name="Milking shed" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{37872FA9-DEFB-4D6F-848C-F92D7B048A75}" name="Feedpad" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{37872FA9-DEFB-4D6F-848C-F92D7B048A75}" name="Feedpad" dataDxfId="48" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_FractionVolatileSolidsVoidedMMS_Data(), Table_SourceData_Dairy_ProductionSystemTemplates[[#Headers],[Area]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9487,10 +9487,10 @@
     <tableColumn id="1" xr3:uid="{D85FDEBC-2FC0-45F1-BCD6-4464E2C22E94}" name="MMS m">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_EFNitrousOxidePerMMS_Data(), Table_SourceData_Dairy_EFm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A21A17E4-5CBE-457C-83F6-E66794AB20C1}" name="EFm" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A21A17E4-5CBE-457C-83F6-E66794AB20C1}" name="EFm" dataDxfId="47" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_EFNitrousOxidePerMMS_Data(), Table_SourceData_Dairy_EFm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0552581B-C2BB-481C-87D1-7C1129F487A9}" name="NIR reference" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{0552581B-C2BB-481C-87D1-7C1129F487A9}" name="NIR reference" dataDxfId="46" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_EFNitrousOxidePerMMS_Data(), Table_SourceData_Dairy_EFm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9509,10 +9509,10 @@
     <tableColumn id="1" xr3:uid="{C1D0CE9E-4549-48D9-9C0F-1310FC73ABC5}" name="Animal class j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_DurationOfStay_Data(), Table_SourceData_Dairy_Duration[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1396CED3-63B3-4B3F-8629-5350DAE232F8}" name="Duration (weaned)" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1396CED3-63B3-4B3F-8629-5350DAE232F8}" name="Duration (weaned)" dataDxfId="45" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_DurationOfStay_Data(), Table_SourceData_Dairy_Duration[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9A35A34C-C373-43B3-B087-AB054A306734}" name="Duration (pre-weaned)" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9A35A34C-C373-43B3-B087-AB054A306734}" name="Duration (pre-weaned)" dataDxfId="44" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_DurationOfStay_Data(), Table_SourceData_Dairy_Duration[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9654,49 +9654,49 @@
     <tableColumn id="1" xr3:uid="{2A59C691-AC40-4CCA-B35C-CFD78C2E4C9E}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{99E1D7C5-8D2F-4BD4-AD41-A5E67D55D21C}" name="MAT" totalsRowDxfId="80" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{99E1D7C5-8D2F-4BD4-AD41-A5E67D55D21C}" name="MAT" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F51DB94D-293B-4C96-AF7B-F23EFFC88169}" name="MAP" totalsRowDxfId="79" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{F51DB94D-293B-4C96-AF7B-F23EFFC88169}" name="MAP" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{69A84A6B-0614-468D-883A-065AC1C309AD}" name="Frost days per year" totalsRowDxfId="78" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{69A84A6B-0614-468D-883A-065AC1C309AD}" name="Frost days per year" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{70B55FBB-C56B-4299-A84F-B56F89FFC7FE}" name="Elevation" totalsRowDxfId="77" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{70B55FBB-C56B-4299-A84F-B56F89FFC7FE}" name="Elevation" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C231F7DC-6BBE-42AD-B9DF-D4944211AD9E}" name="MAP:PET" totalsRowDxfId="76" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{C231F7DC-6BBE-42AD-B9DF-D4944211AD9E}" name="MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{241C1913-B698-47BE-8D1B-EB8066AB574A}" name="Min temp" totalsRowDxfId="75" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{241C1913-B698-47BE-8D1B-EB8066AB574A}" name="Min temp" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D5CBAA08-CC8F-4CF1-9ABB-C802EC4BBD37}" name="Max temp" totalsRowDxfId="74" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{D5CBAA08-CC8F-4CF1-9ABB-C802EC4BBD37}" name="Max temp" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{11BAB109-DF03-401A-9C24-7429B101BE18}" name="Min rainfall" totalsRowDxfId="73" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{11BAB109-DF03-401A-9C24-7429B101BE18}" name="Min rainfall" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{CCF3C75A-B285-49C4-892C-7068170FA4FD}" name="Max rainfall" totalsRowDxfId="72" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{CCF3C75A-B285-49C4-892C-7068170FA4FD}" name="Max rainfall" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{CE6AEE99-C38F-44FA-871B-75F2307F1F67}" name="Min frost days" totalsRowDxfId="71" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{CE6AEE99-C38F-44FA-871B-75F2307F1F67}" name="Min frost days" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{9E5F2F73-F8F3-43CE-ADDF-084E974EA647}" name="Max frost days" totalsRowDxfId="70" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{9E5F2F73-F8F3-43CE-ADDF-084E974EA647}" name="Max frost days" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{90612C07-DACC-4373-9E4C-D4AB615A44A8}" name="Min elevation" totalsRowDxfId="69" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{90612C07-DACC-4373-9E4C-D4AB615A44A8}" name="Min elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{3E3FDCA1-45EA-4B51-810A-C3054F189A56}" name="Max elevation" totalsRowDxfId="68" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{3E3FDCA1-45EA-4B51-810A-C3054F189A56}" name="Max elevation" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{ABFE2712-14EC-4E00-A3EF-18BFDC116010}" name="Min MAP:PET" totalsRowDxfId="67" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{ABFE2712-14EC-4E00-A3EF-18BFDC116010}" name="Min MAP:PET" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{9E863024-D091-4CB7-A1E0-32262C5009E7}" name="Max MAP:PET" totalsRowDxfId="66" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{9E863024-D091-4CB7-A1E0-32262C5009E7}" name="Max MAP:PET" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9714,7 +9714,7 @@
     <tableColumn id="1" xr3:uid="{6BD2B030-4156-459F-AF30-9BAEB721D89B}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E576D2B7-EC3D-416C-B0FF-91FF174BD206}" name="Wet or Dry Zone" totalsRowDxfId="65" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{E576D2B7-EC3D-416C-B0FF-91FF174BD206}" name="Wet or Dry Zone" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9820,7 +9820,7 @@
     <tableColumn id="1" xr3:uid="{D3714B67-D8D4-439D-98F1-8729B044A6D8}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{869F17D9-5786-45E6-A68F-252FA649B4C6}" name="FracWET" dataDxfId="64">
+    <tableColumn id="2" xr3:uid="{869F17D9-5786-45E6-A68F-252FA649B4C6}" name="FracWET" dataDxfId="27">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9868,7 +9868,7 @@
     <tableColumn id="1" xr3:uid="{F40564BD-4773-4D3B-B18C-FAF0EDFEF6CD}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{638B57D5-E778-4A33-B53B-6284589DF37B}" name="FracWET" dataDxfId="63" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{638B57D5-E778-4A33-B53B-6284589DF37B}" name="FracWET" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9898,7 +9898,7 @@
     <tableColumn id="1" xr3:uid="{7FE6DCA1-0C14-4057-B2D5-D9137EDFC6FB}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{83B1E1DE-9642-4980-9CAE-20BCC2AB5061}" name="EFPRP" dataDxfId="62" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{83B1E1DE-9642-4980-9CAE-20BCC2AB5061}" name="EFPRP" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9916,7 +9916,7 @@
     <tableColumn id="1" xr3:uid="{02D7753C-A9D4-4C0F-A50A-1D3B29EA3D15}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B30FE3B4-743B-4444-9E5E-DEDA51B673AB}" name="Season" dataDxfId="61" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B30FE3B4-743B-4444-9E5E-DEDA51B673AB}" name="Season" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9948,49 +9948,49 @@
     <tableColumn id="1" xr3:uid="{FA1DD1C5-8163-4B28-AB74-0293DBC7E04C}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E4ED0FC4-BAC5-4BAE-8410-AB6A99F7168B}" name="MAT (ºC)" dataDxfId="60" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E4ED0FC4-BAC5-4BAE-8410-AB6A99F7168B}" name="MAT (ºC)" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{FD7E363B-6252-4329-AB18-55F0BD2D9C1A}" name="Anaerobic lagoon" dataDxfId="59" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{FD7E363B-6252-4329-AB18-55F0BD2D9C1A}" name="Anaerobic lagoon" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A03DD494-A52F-4BAA-8027-E780FCB4AA27}" name="Digester / covered lagoons" dataDxfId="58" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{A03DD494-A52F-4BAA-8027-E780FCB4AA27}" name="Digester / covered lagoons" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{C99DD533-C85A-4C58-B15A-72CFB230A3D6}" name="Liquid systems" dataDxfId="57" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{C99DD533-C85A-4C58-B15A-72CFB230A3D6}" name="Liquid systems" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{7F51E6DF-AD97-478C-AFBD-9BB66AB1608E}" name="Daily spread" dataDxfId="56" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{7F51E6DF-AD97-478C-AFBD-9BB66AB1608E}" name="Daily spread" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{5125A338-20BE-4F0D-9622-044A8884F086}" name="Composting (passive windrow)" dataDxfId="55" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{5125A338-20BE-4F0D-9622-044A8884F086}" name="Composting (passive windrow)" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5B48328F-6C23-428D-A06A-B327B67635E3}" name="Solid storage" dataDxfId="54" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{5B48328F-6C23-428D-A06A-B327B67635E3}" name="Solid storage" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{059F3E5D-FF00-45D1-9FB8-4938ED7D247A}" name="Pit storage" dataDxfId="53" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{059F3E5D-FF00-45D1-9FB8-4938ED7D247A}" name="Pit storage" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{ACD3805A-CE21-47AD-B824-0877EEC99941}" name="Deep litter" dataDxfId="52" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{ACD3805A-CE21-47AD-B824-0877EEC99941}" name="Deep litter" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D3D1A0CB-1209-4A18-AA2E-E1A46D3090E4}" name="Poultry manure with bedding" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{D3D1A0CB-1209-4A18-AA2E-E1A46D3090E4}" name="Poultry manure with bedding" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{9F6D7D13-09C1-418B-AB18-33464AF1B784}" name="Poultry manure without bedding" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{9F6D7D13-09C1-418B-AB18-33464AF1B784}" name="Poultry manure without bedding" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{6190D71E-99BF-467B-9BF5-7A8A45BA353E}" name="Direct processing" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{6190D71E-99BF-467B-9BF5-7A8A45BA353E}" name="Direct processing" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{05C47416-1D18-4B58-A5F4-7DFB05931801}" name="Direct application" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{05C47416-1D18-4B58-A5F4-7DFB05931801}" name="Direct application" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2330B130-5379-4B5C-82E4-132785F8E066}" name="Pasture range and paddock" dataDxfId="47" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{2330B130-5379-4B5C-82E4-132785F8E066}" name="Pasture range and paddock" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{997A883A-3897-4344-9580-AE7FB9DB6F47}" name="MAT raw" dataDxfId="46" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{997A883A-3897-4344-9580-AE7FB9DB6F47}" name="MAT raw" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10008,7 +10008,7 @@
     <tableColumn id="1" xr3:uid="{8BC80EFA-1F38-4400-9A9D-309999F86408}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B3A4A53F-1B72-4DAC-875F-9E7830626CFD}" name="EFNi &amp; EFN2Oi" dataDxfId="45" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B3A4A53F-1B72-4DAC-875F-9E7830626CFD}" name="EFNi &amp; EFN2Oi" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10024,7 +10024,7 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{D2BD319C-22B4-4CF2-BF13-28AEDC2A576C}" name="Description" dataDxfId="44" dataCellStyle="Content normal"/>
+    <tableColumn id="2" xr3:uid="{D2BD319C-22B4-4CF2-BF13-28AEDC2A576C}" name="Description" dataDxfId="7" dataCellStyle="Content normal"/>
     <tableColumn id="1" xr3:uid="{B38598A2-70B3-4BC6-A603-37557045FBE3}" name="ID"/>
     <tableColumn id="3" xr3:uid="{D870D321-504F-4766-806C-BAEC967A9B0D}" name="Score"/>
   </tableColumns>
@@ -10114,13 +10114,13 @@
     <tableColumn id="1" xr3:uid="{CAC4C566-E7DF-44B3-BDB4-4B1785D5F9F0}" name="Breed">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{4C5541D8-40C3-436A-815B-7A3D9D154BB6}" name="Milking cows" dataDxfId="42" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{4C5541D8-40C3-436A-815B-7A3D9D154BB6}" name="Milking cows" dataDxfId="79" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A8A468F3-E260-4E60-AC14-8F50FD33B46B}" name="Heifers &gt; 1" dataDxfId="41" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{A8A468F3-E260-4E60-AC14-8F50FD33B46B}" name="Heifers &gt; 1" dataDxfId="78" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2081FE2E-69DF-48BF-9561-91AC655332BC}" name="Heifers &lt; 1 (weaned)" dataDxfId="40" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{2081FE2E-69DF-48BF-9561-91AC655332BC}" name="Heifers &lt; 1 (weaned)" dataDxfId="77" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightCowsAndHeifers_Data(), Table_SourceData_Dairy_WjCowsHeifers[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10139,10 +10139,10 @@
     <tableColumn id="1" xr3:uid="{40374F5E-9BC3-4080-A28F-8B1F65DE1774}" name="Breed">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightBulls_Data(), Table_SourceData_Dairy_WjBulls[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C20ABB8A-524B-457C-86CD-D1ADCBCD6339}" name="Bulls &gt; 1" dataDxfId="39" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C20ABB8A-524B-457C-86CD-D1ADCBCD6339}" name="Bulls &gt; 1" dataDxfId="76" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightBulls_Data(), Table_SourceData_Dairy_WjBulls[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7E843FE2-40FC-4270-88C9-9204E6D4AFBC}" name="Bulls &lt; 1 (weaned)" dataDxfId="38" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{7E843FE2-40FC-4270-88C9-9204E6D4AFBC}" name="Bulls &lt; 1 (weaned)" dataDxfId="75" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightBulls_Data(), Table_SourceData_Dairy_WjBulls[[#Headers],[Breed]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10163,16 +10163,16 @@
     <tableColumn id="1" xr3:uid="{69C0AC05-6C13-494A-8124-C36C4B6D01B6}" name="Milking cows">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6F9B3B56-C4EB-4BB7-8805-05635494D786}" name="Heifers &gt; 1" dataDxfId="37" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{6F9B3B56-C4EB-4BB7-8805-05635494D786}" name="Heifers &gt; 1" dataDxfId="74" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9CCB5E7F-697E-47C8-A2FC-07B0CCA18EF6}" name="Heifers &lt; 1 (weaned)" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{9CCB5E7F-697E-47C8-A2FC-07B0CCA18EF6}" name="Heifers &lt; 1 (weaned)" dataDxfId="73" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E2F3229F-1A83-4902-9C97-123E692B43D6}" name="Bulls &gt; 1" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{E2F3229F-1A83-4902-9C97-123E692B43D6}" name="Bulls &gt; 1" dataDxfId="72" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{409BDD9D-D084-43BF-B34D-A29B0DFF00E7}" name="Bulls &lt; 1 (weaned)" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{409BDD9D-D084-43BF-B34D-A29B0DFF00E7}" name="Bulls &lt; 1 (weaned)" dataDxfId="71" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_LiveweightGain_Data(), Table_SourceData_Dairy_LWGj[[#Headers],[Milking cows]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10181,7 +10181,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{296C6784-8B86-412A-92D3-E911DE28757C}" name="Table_SourceData_Dairy_WRj" displayName="Table_SourceData_Dairy_WRj" ref="D54:H55" totalsRowShown="0" headerRowDxfId="33" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{296C6784-8B86-412A-92D3-E911DE28757C}" name="Table_SourceData_Dairy_WRj" displayName="Table_SourceData_Dairy_WRj" ref="D54:H55" totalsRowShown="0" headerRowDxfId="70" headerRowCellStyle="Content normal" dataCellStyle="Content normal">
   <autoFilter ref="D54:H55" xr:uid="{296C6784-8B86-412A-92D3-E911DE28757C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -10211,7 +10211,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{968BB314-DB2C-4CA2-BAA9-E66557777E59}" name="Table_SourceData_Dairy_DataPreWeaned" displayName="Table_SourceData_Dairy_DataPreWeaned" ref="D62:G64" totalsRowShown="0" dataDxfId="32" dataCellStyle="Content normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{968BB314-DB2C-4CA2-BAA9-E66557777E59}" name="Table_SourceData_Dairy_DataPreWeaned" displayName="Table_SourceData_Dairy_DataPreWeaned" ref="D62:G64" totalsRowShown="0" dataDxfId="69" dataCellStyle="Content normal">
   <autoFilter ref="D62:G64" xr:uid="{968BB314-DB2C-4CA2-BAA9-E66557777E59}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -10219,16 +10219,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{598A8529-B449-4014-BE34-ECB667ED42D5}" name="Animal class j" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="1" xr3:uid="{598A8529-B449-4014-BE34-ECB667ED42D5}" name="Animal class j" dataDxfId="68" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C0E8AAB-9E7B-4D2E-B948-D2A0CC665284}" name="CH4 production" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{5C0E8AAB-9E7B-4D2E-B948-D2A0CC665284}" name="CH4 production" dataDxfId="67" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{945A18DE-556C-4BC4-A6F6-B0601941462E}" name="Volatile solids (VSj=3,5)" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{945A18DE-556C-4BC4-A6F6-B0601941462E}" name="Volatile solids (VSj=3,5)" dataDxfId="66" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8FC08B28-B758-4413-861D-9585CC484979}" name="Nitrogen Excreted (NPWj=3,5)" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{8FC08B28-B758-4413-861D-9585CC484979}" name="Nitrogen Excreted (NPWj=3,5)" dataDxfId="65" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_PreWeanedCalves_Data(), Table_SourceData_Dairy_DataPreWeaned[[#Headers],[Animal class j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10254,31 +10254,31 @@
     <tableColumn id="1" xr3:uid="{A54F6170-CD83-454D-874A-2A78490F2BD1}" name="MMS m">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{B29E40EC-DE00-4962-8467-1C7A786C3DE4}" name="ACT" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{B29E40EC-DE00-4962-8467-1C7A786C3DE4}" name="ACT" dataDxfId="64" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1ABF48E7-6948-4398-A069-F461406208B9}" name="NSW" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{1ABF48E7-6948-4398-A069-F461406208B9}" name="NSW" dataDxfId="63" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A3DDB858-97C5-4EC8-955B-D48536431CC8}" name="NT" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{A3DDB858-97C5-4EC8-955B-D48536431CC8}" name="NT" dataDxfId="62" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{64B146B6-1E4C-4E4E-A22B-B3F33B7F2C8D}" name="QLD" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{64B146B6-1E4C-4E4E-A22B-B3F33B7F2C8D}" name="QLD" dataDxfId="61" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4AC061FD-3D5D-4347-80B4-437EEDDA407C}" name="SA" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{4AC061FD-3D5D-4347-80B4-437EEDDA407C}" name="SA" dataDxfId="60" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{58DE1EF2-ABA1-4507-A5A2-10DBB72C5360}" name="TAS" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{58DE1EF2-ABA1-4507-A5A2-10DBB72C5360}" name="TAS" dataDxfId="59" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{BA557B69-47EC-4B41-B9CC-12F16489EFF2}" name="VIC" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{BA557B69-47EC-4B41-B9CC-12F16489EFF2}" name="VIC" dataDxfId="58" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{1830500E-FEC6-4240-A1B1-EB7C6052507D}" name="WA" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{1830500E-FEC6-4240-A1B1-EB7C6052507D}" name="WA" dataDxfId="57" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{32D3BCE1-C338-4B12-B792-DFD9C2DF0EAC}" name="NIR reference" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{32D3BCE1-C338-4B12-B792-DFD9C2DF0EAC}" name="NIR reference" dataDxfId="56" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Dairy.SourceData_Dairy_MCF_Data(), Table_SourceData_Dairy_MCFjm[[#Headers],[MMS m]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -17923,19 +17923,19 @@
         <v>0</v>
       </c>
       <c r="E170" s="52">
-        <f>'Input - Dairy'!F29</f>
+        <f>'Input - Dairy'!F25</f>
         <v>0</v>
       </c>
       <c r="F170" s="52">
-        <f>'Input - Dairy'!G29</f>
+        <f>'Input - Dairy'!G25</f>
         <v>84</v>
       </c>
       <c r="G170" s="52">
-        <f>'Input - Dairy'!H29</f>
+        <f>'Input - Dairy'!H25</f>
         <v>0</v>
       </c>
       <c r="H170" s="52">
-        <f>'Input - Dairy'!I29</f>
+        <f>'Input - Dairy'!I25</f>
         <v>84</v>
       </c>
       <c r="I170" s="54" t="str">
@@ -18300,7 +18300,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O157:R161 D188:F188 N91:P91 E163:H163 F161:I161 N168:Q168 N156:R156 E173:I173 E178:H178 N268 E211 E208 E264 E261 E215 N208 E268 N261 E151:F151 E168:H168 O155:R155 N211 N215 N264 E158:H158 I157:I160 O171:O172 N163:Q163 F171 G174:I176 F176 O176:R176 N178:Q178" xr:uid="{AF7BB680-B75F-4AE8-AA2D-EDF03FCB10D8}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25711,15 +25711,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADQALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAxACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEMAbwB3AHMAIABhAG4AZAAgAEgAZQBpAGYAZQByAHMAIAAoAFcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQwBvAHcAcwAgAGEAbgBkACAASABlAGkAZgBlAHIAcwAgACgAVwBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAARQB4AGMAbAB1AGQAZQBkACAAXAB1ADAAMAAyADcAUgBlAGYAZQByAGUAbgBjAGUAXAB1ADAAMAAyADcALAAgAGEAcwAgAHQAaABlACAAdgBhAGwAdQBlACAAaQBzACAAYwBvAG4AcwBpAHMAdABlAG4AdABsAHkAIABcAHUAMAAwADIANwBEAGEAaQByAHkAIABBAHUAcwB0AHIAYQBsAGkAYQAgAFsAMQBdAFwAdQAwADAAMgA3ACAAYQBuAGQAIABpAHMAIABuAG8AdAAgAHUAcwBlAGQAIABpAG4AIABjAGEAbABjAHUAbABhAHQAaQBvAG4ALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHIAZQBlAGQAXAAiACwAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AZQBkAGkAdQBtACAARgByAGkAZQBzAGkAYQBuAFwAIgAsACAANQA1ADAALAAgADMAOAAwACwAIAAxADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGEAcgBnAGUAIABGAHIAaQBlAHMAaQBhAG4AXAAiACwAIAA2ADAAMAAsACAANAAxADUALAAgADEANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBsAHMAdABlAGkAbgAtAEYAcgBpAGUAcwBpAGEAbgBcACIALAAgADYANQAwACwAIAA0ADUAMAAsACAAMQA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGkAZQBzAGkAYQBuACAAYwByAG8AcwBzAGIAcgBlAGQAXAAiACwAIAA1ADAAMAAsACAAMwA1ADAALAAgADEANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAZQByAHMAZQB5AFwAIgAsACAANAAwADAALAAgADIANwA1ACwAIAAxADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGUAcgBzAGUAeQAgAGMAcgBvAHMAcwBiAHIAZQBkAFwAIgAsACAANAA1ADAALAAgADMAMQA1ACwAIAAxADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHkAcgBzAGgAaQByAGUAXAAiACwAIAA1ADQAMAAsACAAMwA3ADUALAAgADEANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAdQBlAHIAbgBzAGUAeQBcACIALAAgADQAOAAwACwAIAAzADMANQAsACAAMQA0ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAG8AdwBuACAAUwB3AGkAcwBzAFwAIgAsACAANgAwADAALAAgADQAMQA1ACwAIAAxADcAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAGwAbABhAHcAYQByAHIAYQAvAEEAdQBzAHMAaQBlACAAUgBlAGQAXAAiACwAIAA1ADUAMAAsACAAMwA3ADUALAAgADEANQAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAyADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQAgAC0AIABCAHUAbABsAHMAIAAoAFcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQgB1AGwAbABzACAAKABXAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBXAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAGUAZQBkAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABiAHIAZQBlAGQAcwBcACIALAAgADYAMAAwACwAIAAyADIANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMwA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AIAAoAGsAZwApACAAKABMAFcARwBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMwA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AIAAoAGsAZwApACAAKABMAFcARwBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAVwBHAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA1ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABDAG8AdwBzAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAYwAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAwAC4AMAAxADYALAAgADAALgA2ACwAIAAwAC4ANQA3ACwAIAAwAC4AMQAsACAAMAAuADgAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABSAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApACAAKABXAFIAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABSAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApACAAKABXAFIAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBSAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGUAMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAANQA5ADAALAAgADUAOQAwACwAIAA1ADkAMAAsACAANwA3ADAALAAgADcANwAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADUAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEQAYQB0AGEAIABmAG8AcgAgAHAAcgBlACAALQAgAHcAZQBhAG4AZQBkACAAYwBhAGwAdgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA1ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABEAGEAdABhACAAZgBvAHIAIABwAHIAZQAgAC0AIAB3AGUAYQBuAGUAZAAgAGMAYQBsAHYAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBqAD0AMwAsADUAOwAgAE4AUABXAGoAPQAzACwANQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAQQBuAGkAbQBhAGwAIABjAGwAYQBzAHMAIABqAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIABoAGUAYQBkAGUAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABjAGwAYQBzAHMAIABqAFwAIgAsACAAXAAiAEMASAA0ACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgACgAVgBTAGoAPQAzACwANQApAFwAIgAsACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAEUAeABjAHIAZQB0AGUAZAAgACgATgBQAFcAagA9ADMALAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiACgAawBnAC8AZABhAHkAKQBcACIALAAgAFwAIgAoAGsAZwAvAGQAYQB5ACkAXAAiACwAIABcACIAKABrAGcALwBkAGEAeQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzAFwAdQAwADAAMwBjADEAXAAiACwAIAAwAC4AMAAxADcANgAsACAAMAAuADIANgA4ADUALAAgADAALgAwADEAMwA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwBcAHUAMAAwADMAYwAxAFwAIgAsACAAMAAuADAAMgAwADQALAAgADAALgAzADAAMAAzACwAIAAwAC4AMAAwADkAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA2ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABNAEMARgBzACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAagBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA2ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABNAEMARgBzACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAagBtACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBDAEYAagBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA2AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADEAMAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIATgBTAFcAXAAiACwAIABcACIATgBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAFMAQQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBXAEEAXAAiACwAIABcACIATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAMAAuADcAMgAsACAAMAAuADcANgAsACAAMAAuADgALAAgADAALgA3ADgALAAgADAALgA3ADQALAAgADAALgA2ADkALAAgADAALgA3ADMALAAgADAALgA3ADYALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZAAgAC0AIABTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZAAgAC0AIABEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAcwAgACgAYQApAFwAIgAsACAAMAAuADEANQAsACAAMAAuADEAOAAsACAAMAAuADUAMAAsACAAMAAuADIANAAsACAAMAAuADEANwAsACAAMAAuADEAMwAsACAAMAAuADEANwAsACAAMAAuADEAOAAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA3ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIABhAG4AZAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA3ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIABhAG4AZAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAG0AOwAgAEYAcgBhAGMARwBBAFMATQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGUAeABjAHIAZQB0AGUAZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA3AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIALAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGUAeABjAHIAZQB0AGUAZAApAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAxADQAIABQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAsACAAMAAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAxACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgADAALAAgADAALgAzADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMgAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkACAALQAgAFMAdQBtAHAAIABhAG4AZAAgAEQAaQBzAHAAZQByAHMAYQBsAFwAIgAsACAAMAAsACAAMAAuADAANwAsACAAXAAiAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAzACAARABhAGkAbAB5ACAAUwBwAHIAZQBhAGQAIAAtACAARAByAGEAaQBuAHMAIAB0AG8AIABQAGEAZABkAG8AYwBrAFwAIgAsACAAMAAsACAAMAAuADIALAAgAFwAIgBEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAzACAAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAgADAALgAwADAANQAsACAAMAAuADMALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQAgACgATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQAgACgATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFAAVwBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AOABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAQwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBNAFAAVwBFAE4AVABFAFIASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAIAAxACAAeQBlAGEAcgBcACIALAAgADAALgAwADEANwA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQAgAHkAZQBhAHIAXAAiACwAIAAwAC4AMAAyADAANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AOQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAASQBuAGMAcgBlAGEAcwBlAGQAIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrACAAKABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAKQAgACgATQBSAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA5ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABJAG4AYwByAGUAYQBzAGUAZAAgAG0AZQB0AGEAYgBvAGwAaQBjACAAcgBhAHQAZQAgAHcAaABlAG4AIABwAHIAbwBkAHUAYwBpAG4AZwAgAG0AaQBsAGsAIAAoAE0AUgBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUgBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AOQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAQwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBNAFIAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGwAawBpAG4AZwAgAGMAbwB3AHMALAAgAGEAbgBkACAAaABvAHUAcwBlACAAYwBvAHcAcwBcACIALAAgADEALgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwBhAHQAdABsAGUAIABjAGwAYQBzAHMAZQBzAFwAIgAsACAAMQAuADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADAAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdgBvAGkAZABlAGQAIAB0AG8AIABlAGEAYwBoACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAE0AUwBqAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHYAbwBpAGQAZQBkACAAdABvACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBNAFMAagBtACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBqAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEUAeABjAGwAdQBkAGUAZAAgAFwAdQAwADAAMgA3AEEAbgBuAHUAYQBsACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABpAG0AZQAgAHMAcABlAG4AdAAgAHAAZQByACAAYQByAGUAYQBcAHUAMAAwADIANwAgAHIAbwB3ACAAYQBzACAAdABoAGkAcwAgAGkAbgBmAG8AcgBtAGEAdABpAG8AbgAgAGkAcwAgAGkAbgAgAHQAaABlACAAdABhAGIAbABlACAAdABpAHQAbABlAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQByAGUAYQBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE0AaQBsAGsAaQBuAGcAIABTAGgAZQBkAFwAIgAsACAAXAAiAEYAZQBlAGQAcABhAGQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAeQBzAHQAZQBtACAAMQA6ACAARwByAGEAegBlAGQAIABPAG4AbAB5AFwAIgAsACAAMAAuADgAOQAsACAAMAAuADEAMQAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAcwB0AGUAbQAgADIAOgAgAE8AbgAgAGYAZQBlAGQAcABhAGQAIABmAG8AcgAgAFwAdQAwADAAMwBjADEAMAAgAGgAcgAvAGQAYQB5ACAAZgBvAHIAIABcAHUAMAAwADMAYwAzACAAbQBvAG4AdABoAHMALwB5AGUAYQByAFwAIgAsACAAMAAuADcAOQAsACAAMAAuADEAMQAsACAAMAAuADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAcwB0AGUAbQAgADMAOgAgAFAAYQBzAHQAdQByAGUALQBnAHIAYQB6AGUAZAAgADMALQA5ACAAbQBvAG4AdABoAHMALwB5AGUAYQByAFwAIgAsACAAMAAuADUAMwA0ACwAIAAwAC4AMQAxACwAIAAwAC4AMwA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAA0ADoAIABaAGUAcgBvACAAZwByAGEAegBpAG4AZwBcACIALAAgADAALAAgADAALgAxADEALAAgADAALgA4ADkAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARQBGACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAcABlAHIAIABNAE0AUwAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARQBGACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAcABlAHIAIABNAE0AUwAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AXAAiACwAIABcACIATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADEANAAgAFAAYQBzAHQAdQByAGUAXAAiACwAIAAwACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADEAIABBAG4AZQByAG8AYgBpAGMAIABMAGEAZwBvAG8AbgBcACIALAAgADAALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAD0AMgAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkADoAIABTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbABcACIALAAgADAALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAD0AMwAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkADoAIABEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAcwBcACIALAAgADAALAAgAFwAIgBEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQA0ACAAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAgADAALgAwADAANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXABuAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABmAG8AcgAgAGUAYQBjAGgAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGkAbgBwAHUAdAAgAGMAbABhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAZgBvAHIAIABlAGEAYwBoACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AcAB1AHQAIABjAGwAYQBzAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGEAeQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADIAXAB0AEQAQQBUAEEAIAAoAE0ARQBUAEgATwBEACAAMQAgAEEATgBEACAAMgAgAE8AUABUAEkATwBOAFMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABDAG8AbgB2AGUAcgB0AGUAZAAgAGYAcgBlAGUAIAB0AGUAeAB0ACAAaQBuACAAZABvAGMAdQBtAGUAbgB0ACAAdABvACAAdABhAGIAbABlACwAIABtAGEAdABjAGgAaQBuAGcAIABsAGkAdgBlAHMAdABvAGMAawAgAGMAbABhAHMAcwAgAG4AYQBtAGUAcwAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABjAGwAYQBzAHMAIABqAFwAIgAsACAAXAAiAEQAdQByAGEAdABpAG8AbgAgACgAdwBlAGEAbgBlAGQAKQBcACIALAAgAFwAIgBEAHUAcgBhAHQAaQBvAG4AIAAoAHAAcgBlAC0AdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGwAawBpAG4AZwAgAGMAbwB3AHMAXAAiACwAIAAzADYANQAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGUAIAAxACAAeQBlAGEAcgBcACIALAAgADMANgA1ACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAYwAgADEAIAB5AGUAYQByAFwAIgAsACAAMgA4ADEALAAgADgANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAgADEAIAB5AGUAYQByAFwAIgAsACAAMwA2ADUALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGMAIAAxACAAeQBlAGEAcgBcACIALAAgADIAOAAxACwAIAA4ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXABuAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBQAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcAG4ARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABNAEQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADcANQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AFwAbgBOAGUAdAAgAGUAbgBlAHIAZwB5ACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AZQB0ACAAZQBuAGUAcgBnAHkAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ARQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBKACAAbgBlAHQAIABlAG4AZQByAGcAeQAgAC8AIABrAGcAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMwAuADAANQA0ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXABuAEcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABkAHIAeQAgAG0AYQB0AHQAZQByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGQAcgB5ACAAbQBhAHQAdABlAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBFAEMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASgAgAC8AIABrAGcARABNAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMQA4AC4ANAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AFwAbgBFAGYAZgBpAGMAaQBlAG4AYwB5ACAAbwBmACAAdQBzAGUAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBmAGYAaQBjAGkAZQBuAGMAeQAgAG8AZgAgAHUAcwBlACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAA4ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBfAG8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAbQAzACAAQwBIADQALwBrAGcAVgBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AbABlAGEAYwBoAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAxADEAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAG8AcgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABNAE0AUwAgAG8AbgBsAHkAIAAoAGYAcgBhAGMAdABpAG8AbgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAG8AcgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABNAE0AUwAgAG8AbgBsAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAF8ATABFAEEAQwBIAF8ATQBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgBEAGUAZgBhAHUAbAB0ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAB3AGgAZQBuACAAbQBhAG4AdQByAGUAIABpAHMAIABlAHgAYwByAGUAdABlAGQAIAB0AG8AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQAuACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAZQBmAGEAdQBsAHQAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAHcAaABlAG4AIABtAGEAbgB1AHIAZQAgAGkAcwAgAGUAeABjAHIAZQB0AGUAZAAgAHQAbwAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawAgACgAbQA9ADEANAApAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAF8ATABFAEEAQwBIAF8ATQBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAyADQAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHoAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQB6AGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAxACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBcAG4ARgBhAHQAIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBDAF8AagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgBjAGUAbgB0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyACAARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQALgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAFwAbgBQAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAQwBfAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgBjAGUAbgB0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADIAIABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADMALgAzACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMwA6ACAARQBuAHQAZQByAGkAYwAgAE0AZQB0AGgAYQBuAGUAIAAtACAARABhAGkAcgB5ACAAQwBhAHQAdABsAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgAzAC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAARQBuAHQAZQByAGkAYwAgAEQAYQBpAHIAeQAgAEMAYQB0AHQAbABlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AKAAoAE4AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMQAsADIALAA0AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBQAFcAXwB7AEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAxADIANAAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAMQAyADQAIAA9ACAAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANAAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARABfAGoAMQAyADQAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGQAYQB5AHMAKQBcAG4ATgBfAGoAMwA1ACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABoAGUAYQBkACkAXABuAE0AXwBqADMANQAgAD0AIABkAGEAaQBsAHkAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMwAsADUAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEQAXwBqADMANQAgAD0AIABkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBuACAAdABoAGUAIABmAGEAcgBtACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABkAGEAeQBzACkAXABuAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAPQAgAGQAYQBpAGwAeQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqADEAMgA0ACwAIABNAF8AagAxADIANAAsACAARABfAGoAMQAyADQALAAgAE4AXwBqADMANQAsACAATQBfAGoAMwA1ACwAIABEAF8AagAzADUALAAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACwAXABuACAAIAAgACAAKAAoAE4AXwBqADEAMgA0ACAAKgAgAE0AXwBqADEAMgA0ACAAKgAgAEQAXwBqADEAMgA0ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoAMQAyADQALAAgAE0AXwBqADEAMgA0ACwAIABEAF8AagAxADIANAAsACAATgBfAGoAMwA1ACwAIABNAF8AagAzADUALAAgAEQAXwBqADMANQAsACAARABQAFcAXwBqADMANQAsACAATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUALABcAG4AIAAgACAAIAAoACgATgBfAGoAMQAyADQAIAAqACAATQBfAGoAMQAyADQAIAAqACAARABfAGoAMQAyADQAKQAgACsAIAAoAE4AXwBqADMANQAgACoAIABNAF8AagAzADUAIAAqACAARABfAGoAMwA1ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUAIAAqACAARABQAFcAXwBqADMANQApACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBlAG4AdABlAHIAaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqACgAKABOAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADEALAAyACwANAB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AUABXAF8AewBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoACgATgBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAxACwAMgAsADQAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAFAAVwBfAHsARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAFAAVwBfAHsAagA9ADMALAA1AH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqADEAMgA0AFwAIgAsACAAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANABcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAMQAyADQAXAAiACwAIABcACIAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANABcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAMQAyADQAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqADMANQBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAMwA1AFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAdwBlAGEAbgBlAGQAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1AFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADMALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagAzADUAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAdwBlAGEAbgBlAGQAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAFAAVwBfAGoAMwA1AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAHAAcgBlAC0AdwBlAGEAbgBlAGQAIABoAGUAaQBmAGUAcgAgAGEAbgBkACAAYgB1AGwAbAAgAGMAYQBsAHYAZQBzAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcARABQAFcAXAB1ADAAMAAyADcAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAGEAIABzAGUAcABhAHIAYQB0AGUAIABoAGEAbgBkAGwAaQBuAGcAIABvAGYAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAZAB1AHIAYQB0AGkAbwBuAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXABuAE0AXwBqAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAGoAPQAyADAALgA3AFwAXAB0AGkAbQBlAHMAIABJAF8AagBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ASQBfAGoAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABJAF8AagAsAFwAbgAgACAAIAAgADIAMAAuADcAIAAqACAASQBfAGoAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGgAYQByAG0AbABlAHkAIABlAHQAIABhAGwALgAgACgAMgAwADEANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAPQAyADAALgA3AFwAXAB0AGkAbQBlAHMAIABJAF8AagBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALAAgAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBcAG4ARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAbgBJAF8AagBcAG4AawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBJAF8AagA9ACgAMQAuADEAOAA1ACsAMAAuADAAMAA0ADUANABcAFwAdABpAG0AZQBzACAAVwBfAGoALQAwAC4AMAAwADAAMAAwADIANgBcAFwAdABpAG0AZQBzACAAVwBfAGoAXgAyACsAMAAuADMAMQA1AFwAXAB0AGkAbQBlAHMAIABMAFcARwBfAGoAKQBeADIAXABcAHQAaQBtAGUAcwAgAE0AUgBfAGoAKwBNAEkAXwBqAFwAbgBXAF8AagAgAD0AIABsAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQBcAG4ATABXAEcAXwBqACAAPQAgAGwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ATQBSAF8AagAgAD0AIABpAG4AYwByAGUAYQBzAGUAIABpAG4AIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4ATQBJAF8AagAgAD0AIABhAGQAZABpAHQAaQBvAG4AYQBsACAAaQBuAHQAYQBrAGUAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABXAF8AagAsACAATABXAEcAXwBqACwAIABNAFIAXwBqACwAIABNAEkAXwBqACwAXABuACAAIAAgACAAKAAxAC4AMQA4ADUAIAArACAAMAAuADAAMAA0ADUANAAgACoAIABXAF8AagAgAC0AIAAwAC4AMAAwADAAMAAwADIANgAgACoAIABXAF8AagAgAF4AIAAyACAAKwAgADAALgAzADEANQAgACoAIABMAFcARwBfAGoAKQAgAF4AIAAyACAAKgAgAE0AUgBfAGoAIAArACAATQBJAF8AagBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAF8AagA9ACgAMQAuADEAOAA1ACsAMAAuADAAMAA0ADUANABcAFwAdABpAG0AZQBzACAAVwBfAGoALQAwAC4AMAAwADAAMAAwADIANgBcAFwAdABpAG0AZQBzACAAVwBfAGoAXgAyACsAMAAuADMAMQA1AFwAXAB0AGkAbQBlAHMAIABMAFcARwBfAGoAKQBeADIAXABcAHQAaQBtAGUAcwAgAE0AUgBfAGoAKwBNAEkAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAF8AagBcACIALAAgAFwAIgBsAGkAdgBlAHcAZQBpAGcAaAB0AFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAVwBHAF8AagBcACIALAAgAFwAIgBsAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFIAXwBqAFwAIgAsACAAXAAiAGkAbgBjAHIAZQBhAHMAZQAgAGkAbgAgAG0AZQB0AGEAYgBvAGwAaQBjACAAcgBhAHQAZQAgAHcAaABlAG4AIABwAHIAbwBkAHUAYwBpAG4AZwAgAG0AaQBsAGsAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBJAF8AagBcACIALAAgAFwAIgBhAGQAZABpAHQAaQBvAG4AYQBsACAAaQBuAHQAYQBrAGUAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAEEAZABkAGkAdABpAG8AbgBhAGwAIABpAG4AdABhAGsAZQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAE0ASQBfAGoAXABuAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBJAF8AagA9ACgATQBQAF8AagBcAFwAdABpAG0AZQBzACAAMQAuADAAMwBcAFwAdABpAG0AZQBzACAATgBFACkALwAoAEcARQBDAFwAXAB0AGkAbQBlAHMAIABrAFwAXAB0AGkAbQBlAHMAIABxAG0AXwBqACkAXABuAE0AUABfAGoAIAA9ACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAEwALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ATgBFACAAPQAgAG4AZQB0ACAAZQBuAGUAcgBnAHkAIAAoAE0ASgAgAG4AZQB0ACAAZQBuAGUAcgBnAHkALwBrAGcAIABtAGkAbABrACkAXABuAEcARQBDACAAPQAgAGcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgACgATQBKAC8AawBnAEQATQApAFwAbgBrACAAPQAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIAB1AHMAZQAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGYAcgBhAGMAdABpAG8AbgApAFwAbgBxAG0AXwBqACAAPQAgAG0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkAIABvAGYAIAB0AGgAZQAgAGQAaQBlAHQAIAAoAGYAcgBhAGMAdABpAG8AbgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAFAAXwBqACwAIABOAEUALAAgAEcARQBDACwAIABrACwAIABxAG0AXwBqACwAXABuACAAIAAgACAAKABNAFAAXwBqACAAKgAgADEALgAwADMAIAAqACAATgBFACkAIAAvACAAKABHAEUAQwAgACoAIABrACAAKgAgAHEAbQBfAGoAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAEkAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAEkAXwBqAD0AXABcAGYAcgBhAGMAewBNAFAAXwBqAFwAXAB0AGkAbQBlAHMAIAAxAC4AMAAzAFwAXAB0AGkAbQBlAHMAIABOAEUAfQB7AEcARQBDAFwAXAB0AGkAbQBlAHMAIABrAFwAXAB0AGkAbQBlAHMAIABxAG0AXwBqAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBpAG4AcAB1AHQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAXwBqAFwAIgAsACAAXAAiAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABpAGYAIABpAG4AcAB1AHQAIABhAHMAIABsAGkAdAByAGUAcwAgAG8AZgAgAG0AaQBsAGsAKQBcACIALAAgAFwAIgBMAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAF8AagBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAaQBmACAAaQBuAHAAdQB0ACAAYQBzACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACkAXAAiACwAIABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBFAFwAIgAsACAAXAAiAG4AZQB0ACAAZQBuAGUAcgBnAHkAXAAiACwAIABcACIATQBKACAAbgBlAHQAIABlAG4AZQByAGcAeQAvAGsAZwAgAG0AaQBsAGsAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEUAQwBcACIALAAgAFwAIgBnAHIAbwBzAHMAIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAXAAiACwAIABcACIATQBKAC8AawBnAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGsAXAAiACwAIABcACIAZQBmAGYAaQBjAGkAZQBuAGMAeQAgAG8AZgAgAG0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAHUAcwBlACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAG0AXwBqAFwAIgAsACAAXAAiAG0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkAIABvAGYAIAB0AGgAZQAgAGQAaQBlAHQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADMALgAxAC4AMQAgACgANgApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAHUAcwBlACAAbwBmACAAZQBpAHQAaABlAHIAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAIABvAHIAIABsAGkAdAByAGUAcwAgAG8AZgAgAG0AaQBsAGsALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAFwAbgBNAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGMAbwBuAHYAZQByAHQAZQBkACAAZgByAG8AbQAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwBcAG4ATQBQAF8AagBcAG4ATAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBQAF8AagA9AE0AUwBfAGoALwAoADAALgAwADEAXABcAHQAaQBtAGUAcwAgACgARgBDAF8AagArAFAAQwBfAGoAKQApAFwAbgBNAFMAXwBqACAAPQAgAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAIAAoAGsAZwAgAE0AUwAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBGAEMAXwBqACAAPQAgAGYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4AUABDAF8AagAgAD0AIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAFMAXwBqACwAIABGAEMAXwBqACwAIABQAEMAXwBqACwAXABuACAAIAAgACAATQBTAF8AagAgAC8AIAAoADAALgAwADEAIAAqACAAKABGAEMAXwBqACAAKwAgAFAAQwBfAGoAKQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAYwBvAG4AdgBlAHIAdABlAGQAIABmAHIAbwBtACAAbQBpAGwAawAgAHMAbwBsAGkAZABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBQAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBQAF8AagA9AFwAXABmAHIAYQBjAHsATQBTAF8AagB9AHsAMAAuADAAMQBcAFwAdABpAG0AZQBzACAAKABGAEMAXwBqACsAUABDAF8AagApAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUABVAFwAIgAsACAAXAAiAGkAbgBwAHUAdAAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAdQBuAGkAdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUwBfAGoAXAAiACwAIABcACIAZABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwBcACIALAAgAFwAIgBrAGcAIABNAFMALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEMAXwBqAFwAIgAsACAAXAAiAGYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAQwBfAGoAXAAiACwAIABcACIAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUABVAFwAIgAsACAAXAAiAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAdQBuAGkAdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUwBfAGoAXAAiACwAIABcACIAZABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwBcACIALAAgAFwAIgBrAGcAIABNAFMALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEMAXwBqAFwAIgAsACAAXAAiAGYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAQwBfAGoAXAAiACwAIABcACIAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAdQBuAGkAdAAgAHYAYQByAGkAYQBiAGwAZQAgAHQAbwAgAGEAbABsAG8AdwAgAGYAbwByACAAdQBzAGUAIABvAGYAIABlAGkAdABoAGUAcgAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwAgAG8AcgAgAGwAaQB0AHIAZQBzACAAbwBmACAAbQBpAGwAawAuACAAQwBvAG4AdgBlAHIAdABlAGQAIABpAG4AcAB1AHQAIABGAEMAIABhAG4AZAAgAFAAQwAgAHAAZQByAGMAZQBuAHQAIAB0AG8AIABpAG4AdABlAGcAZQByAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABcAG4ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQAgAG8AZgAgAGQAaQBlAHQAXABuAHEAbQBfAGoAXABuAGYAcgBhAGMAdABpAG8AbgBcAG4AcQBtAF8AagA9ADAALgA3ADkANQBcAFwAdABpAG0AZQBzACAAKABEAE0ARABfAGoAXABcAHQAaQBtAGUAcwAgADEAMAAwACkALQAwAC4AMAAwADEANABcAG4ARABNAEQAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAZQB4AHAAcgBlAHMAcwBlAGQAIABhAHMAIABhACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQATQBEAF8AagAsAFwAbgAgACAAIAAgADAALgA3ADkANQAgACoAIAAoAEQATQBEAF8AagAgACoAIAAxADAAMAApACAALQAgADAALgAwADAAMQA0AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABNAEQAXwBqACwAXABuACAAIAAgACAAMAAuADAAMAA3ADkANQAgACoAIAAoAEQATQBEAF8AagAgACoAIAAxADAAMAApACAALQAgADAALgAwADAAMQA0AFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAZABpAGUAdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHEAbQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcQBtAF8AagA9ADAALgA3ADkANQBcAFwAdABpAG0AZQBzACAAKABEAE0ARABfAGoAXABcAHQAaQBtAGUAcwAgADEAMAAwACkALQAwAC4AMAAwADEANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBxAG0AXwBqAD0AMAAuADAAMAA3ADkANQBcAFwAdABpAG0AZQBzACAAKABEAE0ARABfAGoAXABcAHQAaQBtAGUAcwAgADEAMAAwACkALQAwAC4AMAAwADEANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABNAEQAXwBqAFwAIgAsACAAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAZQB4AHAAcgBlAHMAcwBlAGQAIABhAHMAIABhACAAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABjAGgAYQBuAGcAZQBkACAAMAAuADcAOQA1ACAAdABvACAAMAAuADAAMAA3ADkANQAgAHcAaABpAGMAaAAgAGkAcwAgAHQAaABlACAAdgBhAGwAdQBlACAAdQBzAGUAZAAgAGkAbgAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdABcACIAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAXwBEAGEAaQByAHkAIgAsACIAdABlAHgAdAAiADoAIgBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4ASQBuAE0ATQBTAEEAZgB0AGUAcgBTAG8AbABpAGQAUwBlAHAAYQByAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAE0ATQBTAEYAcgBhAGMAdABpAG8AbgAsACAARgByAGEAYwB0AGkAbwBuAFMAZQBwAGEAcgBhAHQAZQBkACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAgACoAIAAoAE0ATQBTAEYAcgBhAGMAdABpAG8AbgAtACgATQBNAFMARgByAGEAYwB0AGkAbwBuACoARgByAGEAYwB0AGkAbwBuAFMAZQBwAGEAcgBhAHQAZQBkACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAbgBpAHQAYQBsAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAEYAcgBhAGMAdABpAG8AbgAsAFwAbgAgACAAIAAgAE0ATQBTADEARgByAGEAYwB0AGkAbwBuACwAIABNAE0AUwAxAFMAZQBwAGEAcgBhAHQAZQBkACwAIABcAG4AIAAgACAAIABNAE0AUwAyAEYAcgBhAGMAdABpAG8AbgAsACAATQBNAFMAMgBTAGUAcABhAHIAYQB0AGUAZAAsACAAXABuACAAIAAgACAATQBNAFMAMwBGAHIAYQBjAHQAaQBvAG4ALAAgAE0ATQBTADMAUwBlAHAAYQByAGEAdABlAGQALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACAAKgAgACgAXABuACAAIAAgACAAIAAgACAAIABJAG4AaQB0AGEAbABTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBGAHIAYQBjAHQAaQBvAG4AIAArAFwAbgAgACAAIAAgACAAIAAgACAAKABNAE0AUwAxAEYAcgBhAGMAdABpAG8AbgAgACoAIABNAE0AUwAxAFMAZQBwAGEAcgBhAHQAZQBkACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAKABNAE0AUwAyAEYAcgBhAGMAdABpAG8AbgAgACoAIABNAE0AUwAyAFMAZQBwAGEAcgBhAHQAZQBkACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAKABNAE0AUwAzAEYAcgBhAGMAdABpAG8AbgAgACoAIABNAE0AUwAzAFMAZQBwAGEAcgBhAHQAZQBkACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUASABhAHIAdgBlAHMAdABJAG4AZABlAHgAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwBfAEQAYQBpAHIAeQAuAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBJAG4ATQBNAFMAQQBmAHQAZQByAFMAbwBsAGkAZABTAGUAcABhAHIAYQB0AGkAbwBuACIALAAiAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwBfAEQAYQBpAHIAeQAuAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -25914,30 +25920,35 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADQALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAxACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIABmAG8AcgAgAG0AYQBuAHUAZgBhAGMAdAB1AHIAaQBuAGcAIABiAGUAZQBmAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAdABsAGUALAAgAGYAbwByACAAcAByAGkAbQBlACAAYgBlAGUAZgBcACIALAAgAFwAIgBOAFMAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AHQAbABlACwAIAB3AGUAYQBuAGUAcgBzAFwAIgAsACAAXAAiAE4AVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFEATABEAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBWAEkAQwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFcAQQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBoAGkAYwBrAGUAbgBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQAgAHIAZQBnAGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABwAHIAbwBkAHUAYwB0AHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBWAGEAaQByAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATABpAGYAZQBjAHkAYwBsAGUAcwAuACAAKAAyADAAMgA2ACkALgAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABHAGEAcwAgAEUAbQBpAHMAcwBpAG8AbgAgAEkAbgB0AGUAbgBzAGkAdABpAGUAcwAgAGYAbwByACAATQBhAHQAZQByAGkAYQBsACAASQBuAHAAdQB0AHMAIAB0AG8AIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5AC4AIABWAGUAcgBzAGkAbwBuACAANAA4AC4AIABkAG8AaQAgADEAMAAuADUAMgA4ADEALwB6AGUAbgBvAGQAbwAuADEAOQA2ADUANgA1ADgAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlACAAcgBlAGcAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQByAHkAIABjAG8AdwBzAFwAIgAsACAAXAAiAFYASQBDAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAGkAZwBzACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUABpAGcAcwBfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAaQBmAGUAYwB5AGMAbABlAHMALgAgACgAMgAwADIANgApAC4AIABHAHIAZQBlAG4AaABvAHUAcwBlACAARwBhAHMAIABFAG0AaQBzAHMAaQBvAG4AIABJAG4AdABlAG4AcwBpAHQAaQBlAHMAIABmAG8AcgAgAE0AYQB0AGUAcgBpAGEAbAAgAEkAbgBwAHUAdABzACAAdABvACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAuACAAVgBlAHIAcwBpAG8AbgAgADQAOAAuACAAZABvAGkAIAAxADAALgA1ADIAOAAxAC8AegBlAG4AbwBkAG8ALgAxADkANgA1ADYANQA4ADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAaABlAGUAcAAgAHAAcgBvAGQAdQBjAHQAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGkAZgBlAGMAeQBjAGwAZQBzAC4AIAAoADIAMAAyADYAKQAuACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEcAYQBzACAARQBtAGkAcwBzAGkAbwBuACAASQBuAHQAZQBuAHMAaQB0AGkAZQBzACAAZgBvAHIAIABNAGEAdABlAHIAaQBhAGwAIABJAG4AcAB1AHQAcwAgAHQAbwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkALgAgAFYAZQByAHMAaQBvAG4AIAA0ADgALgAgAGQAbwBpACAAMQAwAC4ANQAyADgAMQAvAHoAZQBuAG8AZABvAC4AMQA5ADYANQA2ADUAOAAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAIAByAGUAZwBpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABtAHUAdAB0AG8AbgBcACIALAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABlAGUAcAAsACAAZgBvAHIAIABwAHIAaQBtAGUAIABsAGEAbQBiAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBTAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAVwBBAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIATwBXACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACAALQAgADEAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwALABcAG4AIAAgAEMATwBMAFUATQBOACgAVABhAGIAbABlAEgAZQBhAGQAZQByAEMAZQBsAGwAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIABBAHIAcgBhAHkARABhAHQAYQAsACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALAAgAFsAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQBdACwAXABuACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAASQBOAEQARQBYACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFUATgBJAFEAVQBFACgAQQByAHIAYQB5AEQAYQB0AGEAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkALAAgADEALAAgAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALAAgAFwAIgBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACAAIAAgACAAKQAsACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQAsACAAMAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIAAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADEAKQAqACgATABvAG8AawB1AHAAQQByAHIAYQB5ADIAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgApACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkARgBGAGEAbABzAGUAKQApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGUAbABsACwAIABEAGUAbABpAG0AaQB0AGUAcgAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQBdACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyAF0ALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSAFgATQBMACgAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMAdABcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwBzAFwAdQAwADAAMwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgACkAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMALwB0AFwAdQAwADAAMwBlAFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZQBsAGUAdgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AbQBhAHAAXwBwAGUAdAApACwAXABuACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQBcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATQBpAG4AQQByAHIAYQB5ACwAIABNAGEAeABBAHIAcgBhAHkALAAgAEkAdABlAG0AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBpAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGEAeABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlACwAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAB1ADAAMAAyADcAXAAiACAAXAB1ADAAMAAyADYAIABzAGgAIABcAHUAMAAwADIANgAgAFwAIgBcAHUAMAAwADIANwAhAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBEAGkAZgBmAGUAcgBlAG4AdABTAGgAZQBlAHQAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADEAXwAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMQAsACAAMgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAZwB1AG0AZQBuAHQAcwBfADMAXwA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAQwBIAE8ATwBTAEUAQwBPAEwAUwAoAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsACAAMwAsACAANAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEcAZQB0AE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABNAE0AUwAsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABNAEUARABJAEEATgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVQBOAEQAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgADAAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABpAHQAbABlAEMAZQBsAGwALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwALABcAG4AIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgATABFAEYAVAAoAFMAbwB1AHIAYwBlAEMAZQBsAGwALAAgAEYASQBOAEQAKABcACIALABcACIALAAgAFMAbwB1AHIAYwBlAEMAZQBsAGwAKQAgAC0AMQApACwAIABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAXAAiACwAIABcACIAXAAiACkAIABcAHUAMAAwADIANgAgAFwAIgAgAFwAIgAgAFwAdQAwADAAMgA2ACAAVABpAHQAbABlAEMAZQBsAGwAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAIAAoAGsAZwApACAALQAgAEMAbwB3AHMAIABhAG4AZAAgAEgAZQBpAGYAZQByAHMAIAAoAFcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQwBvAHcAcwAgAGEAbgBkACAASABlAGkAZgBlAHIAcwAgACgAVwBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAARQB4AGMAbAB1AGQAZQBkACAAXAB1ADAAMAAyADcAUgBlAGYAZQByAGUAbgBjAGUAXAB1ADAAMAAyADcALAAgAGEAcwAgAHQAaABlACAAdgBhAGwAdQBlACAAaQBzACAAYwBvAG4AcwBpAHMAdABlAG4AdABsAHkAIABcAHUAMAAwADIANwBEAGEAaQByAHkAIABBAHUAcwB0AHIAYQBsAGkAYQAgAFsAMQBdAFwAdQAwADAAMgA3ACAAYQBuAGQAIABpAHMAIABuAG8AdAAgAHUAcwBlAGQAIABpAG4AIABjAGEAbABjAHUAbABhAHQAaQBvAG4ALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHIAZQBlAGQAXAAiACwAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AZQBkAGkAdQBtACAARgByAGkAZQBzAGkAYQBuAFwAIgAsACAANQA1ADAALAAgADMAOAAwACwAIAAxADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGEAcgBnAGUAIABGAHIAaQBlAHMAaQBhAG4AXAAiACwAIAA2ADAAMAAsACAANAAxADUALAAgADEANwAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBsAHMAdABlAGkAbgAtAEYAcgBpAGUAcwBpAGEAbgBcACIALAAgADYANQAwACwAIAA0ADUAMAAsACAAMQA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGkAZQBzAGkAYQBuACAAYwByAG8AcwBzAGIAcgBlAGQAXAAiACwAIAA1ADAAMAAsACAAMwA1ADAALAAgADEANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAZQByAHMAZQB5AFwAIgAsACAANAAwADAALAAgADIANwA1ACwAIAAxADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGUAcgBzAGUAeQAgAGMAcgBvAHMAcwBiAHIAZQBkAFwAIgAsACAANAA1ADAALAAgADMAMQA1ACwAIAAxADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHkAcgBzAGgAaQByAGUAXAAiACwAIAA1ADQAMAAsACAAMwA3ADUALAAgADEANQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAdQBlAHIAbgBzAGUAeQBcACIALAAgADQAOAAwACwAIAAzADMANQAsACAAMQA0ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAG8AdwBuACAAUwB3AGkAcwBzAFwAIgAsACAANgAwADAALAAgADQAMQA1ACwAIAAxADcAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAGwAbABhAHcAYQByAHIAYQAvAEEAdQBzAHMAaQBlACAAUgBlAGQAXAAiACwAIAA1ADUAMAAsACAAMwA3ADUALAAgADEANQAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAyADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQAgAC0AIABCAHUAbABsAHMAIAAoAFcAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMgA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAIAAtACAAQgB1AGwAbABzACAAKABXAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBXAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgByAGUAZQBkAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABiAHIAZQBlAGQAcwBcACIALAAgADYAMAAwACwAIAAyADIANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AMwA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AIAAoAGsAZwApACAAKABMAFcARwBqACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMwA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAATABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AIAAoAGsAZwApACAAKABMAFcARwBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAVwBHAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA1ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBsAGsAaQBuAGcAIABDAG8AdwBzAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAYwAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAwAC4AMAAxADYALAAgADAALgA2ACwAIAAwAC4ANQA3ACwAIAAwAC4AMQAsACAAMAAuADgAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABSAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApACAAKABXAFIAagApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABSAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApACAAKABXAFIAagApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVwBSAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGUAMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAANQA5ADAALAAgADUAOQAwACwAIAA1ADkAMAAsACAANwA3ADAALAAgADcANwAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADUAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEQAYQB0AGEAIABmAG8AcgAgAHAAcgBlACAALQAgAHcAZQBhAG4AZQBkACAAYwBhAGwAdgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA1ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABEAGEAdABhACAAZgBvAHIAIABwAHIAZQAgAC0AIAB3AGUAYQBuAGUAZAAgAGMAYQBsAHYAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBqAD0AMwAsADUAOwAgAE4AUABXAGoAPQAzACwANQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAQQBuAGkAbQBhAGwAIABjAGwAYQBzAHMAIABqAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIABoAGUAYQBkAGUAcgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABjAGwAYQBzAHMAIABqAFwAIgAsACAAXAAiAEMASAA0ACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgACgAVgBTAGoAPQAzACwANQApAFwAIgAsACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAEUAeABjAHIAZQB0AGUAZAAgACgATgBQAFcAagA9ADMALAA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiACgAawBnAC8AZABhAHkAKQBcACIALAAgAFwAIgAoAGsAZwAvAGQAYQB5ACkAXAAiACwAIABcACIAKABrAGcALwBkAGEAeQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzAFwAdQAwADAAMwBjADEAXAAiACwAIAAwAC4AMAAxADcANgAsACAAMAAuADIANgA4ADUALAAgADAALgAwADEAMwA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwBcAHUAMAAwADMAYwAxAFwAIgAsACAAMAAuADAAMgAwADQALAAgADAALgAzADAAMAAzACwAIAAwAC4AMAAwADkAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA2ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABNAEMARgBzACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAagBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA2ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABNAEMARgBzACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAagBtACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBDAEYAagBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA2AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADEAMAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIATgBTAFcAXAAiACwAIABcACIATgBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAFMAQQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBXAEEAXAAiACwAIABcACIATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAMAAuADcAMgAsACAAMAAuADcANgAsACAAMAAuADgALAAgADAALgA3ADgALAAgADAALgA3ADQALAAgADAALgA2ADkALAAgADAALgA3ADMALAAgADAALgA3ADYALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZAAgAC0AIABTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADUALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADUALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZAAgAC0AIABEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAcwAgACgAYQApAFwAIgAsACAAMAAuADEANQAsACAAMAAuADEAOAAsACAAMAAuADUAMAAsACAAMAAuADIANAAsACAAMAAuADEANwAsACAAMAAuADEAMwAsACAAMAAuADEANwAsACAAMAAuADEAOAAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA3ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIABhAG4AZAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA3ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIABhAG4AZAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAG0AOwAgAEYAcgBhAGMARwBBAFMATQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGUAeABjAHIAZQB0AGUAZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgA3AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIALAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AbQAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgAgAGUAeABjAHIAZQB0AGUAZAApAFwAIgAsACAAXAAiAE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAxADQAIABQAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAsACAAMAAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAxACAAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAgADAALAAgADAALgAzADUALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAD0AMgAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkACAALQAgAFMAdQBtAHAAIABhAG4AZAAgAEQAaQBzAHAAZQByAHMAYQBsAFwAIgAsACAAMAAsACAAMAAuADAANwAsACAAXAAiAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAzACAARABhAGkAbAB5ACAAUwBwAHIAZQBhAGQAIAAtACAARAByAGEAaQBuAHMAIAB0AG8AIABQAGEAZABkAG8AYwBrAFwAIgAsACAAMAAsACAAMAAuADIALAAgAFwAIgBEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0APQAzACAAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAgADAALgAwADAANQAsACAAMAAuADMALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQAgACgATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADgAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQAgACgATQBQAFcARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAFAAVwBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AOABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAQwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBNAFAAVwBFAE4AVABFAFIASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAIAAxACAAeQBlAGEAcgBcACIALAAgADAALgAwADEANwA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQAgAHkAZQBhAHIAXAAiACwAIAAwAC4AMAAyADAANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBcAG4AVABhAGIAbABlACAAQQAuADEALgAzAC4AOQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAASQBuAGMAcgBlAGEAcwBlAGQAIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrACAAKABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAKQAgACgATQBSAGoAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgA5ADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABJAG4AYwByAGUAYQBzAGUAZAAgAG0AZQB0AGEAYgBvAGwAaQBjACAAcgBhAHQAZQAgAHcAaABlAG4AIABwAHIAbwBkAHUAYwBpAG4AZwAgAG0AaQBsAGsAIAAoAE0AUgBqACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AUgBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AOQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAAQwBsAGEAcwBzACAAagBcACIALAAgAFwAIgBNAFIAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGwAawBpAG4AZwAgAGMAbwB3AHMALAAgAGEAbgBkACAAaABvAHUAcwBlACAAYwBvAHcAcwBcACIALAAgADEALgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwBhAHQAdABsAGUAIABjAGwAYQBzAHMAZQBzAFwAIgAsACAAMQAuADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADAAOgAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdgBvAGkAZABlAGQAIAB0AG8AIABlAGEAYwBoACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAE0AUwBqAG0AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAwADoAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHYAbwBpAGQAZQBkACAAdABvACAAZQBhAGMAaAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBNAFMAagBtACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBqAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADMALgAxADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEUAeABjAGwAdQBkAGUAZAAgAFwAdQAwADAAMgA3AEEAbgBuAHUAYQBsACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABpAG0AZQAgAHMAcABlAG4AdAAgAHAAZQByACAAYQByAGUAYQBcAHUAMAAwADIANwAgAHIAbwB3ACAAYQBzACAAdABoAGkAcwAgAGkAbgBmAG8AcgBtAGEAdABpAG8AbgAgAGkAcwAgAGkAbgAgAHQAaABlACAAdABhAGIAbABlACAAdABpAHQAbABlAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQByAGUAYQBcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE0AaQBsAGsAaQBuAGcAIABTAGgAZQBkAFwAIgAsACAAXAAiAEYAZQBlAGQAcABhAGQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAeQBzAHQAZQBtACAAMQA6ACAARwByAGEAegBlAGQAIABPAG4AbAB5AFwAIgAsACAAMAAuADgAOQAsACAAMAAuADEAMQAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAcwB0AGUAbQAgADIAOgAgAE8AbgAgAGYAZQBlAGQAcABhAGQAIABmAG8AcgAgAFwAdQAwADAAMwBjADEAMAAgAGgAcgAvAGQAYQB5ACAAZgBvAHIAIABcAHUAMAAwADMAYwAzACAAbQBvAG4AdABoAHMALwB5AGUAYQByAFwAIgAsACAAMAAuADcAOQAsACAAMAAuADEAMQAsACAAMAAuADEAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAcwB0AGUAbQAgADMAOgAgAFAAYQBzAHQAdQByAGUALQBnAHIAYQB6AGUAZAAgADMALQA5ACAAbQBvAG4AdABoAHMALwB5AGUAYQByAFwAIgAsACAAMAAuADUAMwA0ACwAIAAwAC4AMQAxACwAIAAwAC4AMwA1ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AHMAdABlAG0AIAA0ADoAIABaAGUAcgBvACAAZwByAGEAegBpAG4AZwBcACIALAAgADAALAAgADAALgAxADEALAAgADAALgA4ADkAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARQBGACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAcABlAHIAIABNAE0AUwAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEALgAxAC4AMwAuADEAMQA6ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAAtACAARQBGACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAcABlAHIAIABNAE0AUwAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAbQApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAbQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAzAC4AMQAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAcgBlAGYAZQByAGUAbgBjAGUAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMwAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AXAAiACwAIABcACIATgBJAFIAIAByAGUAZgBlAHIAZQBuAGMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADEANAAgAFAAYQBzAHQAdQByAGUAXAAiACwAIAAwACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbQA9ADEAIABBAG4AZQByAG8AYgBpAGMAIABMAGEAZwBvAG8AbgBcACIALAAgADAALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAD0AMgAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkADoAIABTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbABcACIALAAgADAALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBtAD0AMwAgAEQAYQBpAGwAeQAgAFMAcAByAGUAYQBkADoAIABEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAcwBcACIALAAgADAALAAgAFwAIgBEAHIAYQBpAG4AcwAgAHQAbwAgAHAAYQBkAGQAbwBjAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG0APQA0ACAAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAgADAALgAwADAANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXABuAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABmAG8AcgAgAGUAYQBjAGgAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGkAbgBwAHUAdAAgAGMAbABhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAZgBvAHIAIABlAGEAYwBoACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AcAB1AHQAIABjAGwAYQBzAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGEAeQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADIAXAB0AEQAQQBUAEEAIAAoAE0ARQBUAEgATwBEACAAMQAgAEEATgBEACAAMgAgAE8AUABUAEkATwBOAFMAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFADoAIABDAG8AbgB2AGUAcgB0AGUAZAAgAGYAcgBlAGUAIAB0AGUAeAB0ACAAaQBuACAAZABvAGMAdQBtAGUAbgB0ACAAdABvACAAdABhAGIAbABlACwAIABtAGEAdABjAGgAaQBuAGcAIABsAGkAdgBlAHMAdABvAGMAawAgAGMAbABhAHMAcwAgAG4AYQBtAGUAcwAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADMALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABjAGwAYQBzAHMAIABqAFwAIgAsACAAXAAiAEQAdQByAGEAdABpAG8AbgAgACgAdwBlAGEAbgBlAGQAKQBcACIALAAgAFwAIgBEAHUAcgBhAHQAaQBvAG4AIAAoAHAAcgBlAC0AdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGwAawBpAG4AZwAgAGMAbwB3AHMAXAAiACwAIAAzADYANQAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGUAIAAxACAAeQBlAGEAcgBcACIALAAgADMANgA1ACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAYwAgADEAIAB5AGUAYQByAFwAIgAsACAAMgA4ADEALAAgADgANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAgADEAIAB5AGUAYQByAFwAIgAsACAAMwA2ADUALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGMAIAAxACAAeQBlAGEAcgBcACIALAAgADIAOAAxACwAIAA4ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXABuAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABmAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBQAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcAG4ARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARABNAEQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyAFwAdABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADcANQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AFwAbgBOAGUAdAAgAGUAbgBlAHIAZwB5ACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AZQB0ACAAZQBuAGUAcgBnAHkAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4ARQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBKACAAbgBlAHQAIABlAG4AZQByAGcAeQAgAC8AIABrAGcAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMwAuADAANQA0ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXABuAEcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABkAHIAeQAgAG0AYQB0AHQAZQByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwByAG8AcwBzACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAZgBlAGUAZAAgAGQAcgB5ACAAbQBhAHQAdABlAHIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBFAEMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ASgAgAC8AIABrAGcARABNAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAMwAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMQA4AC4ANAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AFwAbgBFAGYAZgBpAGMAaQBlAG4AYwB5ACAAbwBmACAAdQBzAGUAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBmAGYAaQBjAGkAZQBuAGMAeQAgAG8AZgAgAHUAcwBlACAAbwBmACAAbQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQAgAGUAbgBlAHIAZwB5ACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAA4ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4AQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBfAG8AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAbQAzACAAQwBIADQALwBrAGcAVgBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AbABlAGEAYwBoAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAzAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMAAxADEAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAG8AcgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABNAE0AUwAgAG8AbgBsAHkAIAAoAGYAcgBhAGMAdABpAG8AbgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAG8AcgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABNAE0AUwAgAG8AbgBsAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAF8ATABFAEEAQwBIAF8ATQBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgBEAGUAZgBhAHUAbAB0ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAB3AGgAZQBuACAAbQBhAG4AdQByAGUAIABpAHMAIABlAHgAYwByAGUAdABlAGQAIAB0AG8AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQAuACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAZQBmAGEAdQBsAHQAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAHcAaABlAG4AIABtAGEAbgB1AHIAZQAgAGkAcwAgAGUAeABjAHIAZQB0AGUAZAAgAHQAbwAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawAgACgAbQA9ADEANAApAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAF8ATABFAEEAQwBIAF8ATQBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADMALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAyADQAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHoAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQB6AGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMwAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMgAxACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBcAG4ARgBhAHQAIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBDAF8AagBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgBjAGUAbgB0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADIALgAyACAARABBAFQAQQAgACgATQBFAFQASABPAEQAIAAxACAAQQBOAEQAIAAyACAATwBQAFQASQBPAE4AUwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADQALgAwACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAFwAbgBQAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAHQAZQBpAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAZgBhAHQAIABhAG4AZAAgAHAAcgBvAHQAZQBpAG4AIABjAG8AcgByAGUAYwB0AGUAZAAgAG0AaQBsAGsAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAQwBfAGoAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgBjAGUAbgB0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMgAuADIAIABEAEEAVABBACAAKABNAEUAVABIAE8ARAAgADEAIABBAE4ARAAgADIAIABPAFAAVABJAE8ATgBTACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADMALgAzACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAzAC4AMwA6ACAARQBuAHQAZQByAGkAYwAgAE0AZQB0AGgAYQBuAGUAIAAtACAARABhAGkAcgB5ACAAQwBhAHQAdABsAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADMALgAzAC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAARQBuAHQAZQByAGkAYwAgAEQAYQBpAHIAeQAgAEMAYQB0AHQAbABlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABlAG4AdABlAHIAaQBjACAAZgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AIABpAG4AIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQBcAG4ARQBfAGUAbgB0AGUAcgBpAGMAXABuAHQAIABDAEgANABcAG4ARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AKAAoAE4AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMQAsADIALAA0AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAF8AewBqAD0AMwAsADUAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBQAFcAXwB7AEUATgBUAEUAUgBJAEMALABqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBOAF8AagAxADIANAAgAD0AIABuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGgAZQBhAGQAKQBcAG4ATQBfAGoAMQAyADQAIAA9ACAAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANAAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ARABfAGoAMQAyADQAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAIAAoAGQAYQB5AHMAKQBcAG4ATgBfAGoAMwA1ACAAPQAgAG4AdQBtAGIAZQByACAAbwBmACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABoAGUAYQBkACkAXABuAE0AXwBqADMANQAgAD0AIABkAGEAaQBsAHkAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAGMAbABhAHMAcwBlAHMAIABqAD0AMwAsADUAIAAoAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAEQAXwBqADMANQAgAD0AIABkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBuACAAdABoAGUAIABmAGEAcgBtACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1ACAAKABkAGEAeQBzACkAXABuAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAPQAgAGQAYQBpAGwAeQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAaABlAGkAZgBlAHIAIABhAG4AZAAgAGIAdQBsAGwAIABjAGEAbAB2AGUAcwAgACgAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE4AXwBqADEAMgA0ACwAIABNAF8AagAxADIANAAsACAARABfAGoAMQAyADQALAAgAE4AXwBqADMANQAsACAATQBfAGoAMwA1ACwAIABEAF8AagAzADUALAAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACwAXABuACAAIAAgACAAKAAoAE4AXwBqADEAMgA0ACAAKgAgAE0AXwBqADEAMgA0ACAAKgAgAEQAXwBqADEAMgA0ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACAAKwAgACgATgBfAGoAMwA1ACAAKgAgAE0AUABXAF8ARQBOAFQARQBSAEkAQwBfAGoAMwA1ACAAKgAgAEQAXwBqADMANQApACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATgBfAGoAMQAyADQALAAgAE0AXwBqADEAMgA0ACwAIABEAF8AagAxADIANAAsACAATgBfAGoAMwA1ACwAIABNAF8AagAzADUALAAgAEQAXwBqADMANQAsACAARABQAFcAXwBqADMANQAsACAATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUALABcAG4AIAAgACAAIAAoACgATgBfAGoAMQAyADQAIAAqACAATQBfAGoAMQAyADQAIAAqACAARABfAGoAMQAyADQAKQAgACsAIAAoAE4AXwBqADMANQAgACoAIABNAF8AagAzADUAIAAqACAARABfAGoAMwA1ACkAIAArACAAKABOAF8AagAzADUAIAAqACAATQBQAFcAXwBFAE4AVABFAFIASQBDAF8AagAzADUAIAAqACAARABQAFcAXwBqADMANQApACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZQBuAHQAZQByAGkAYwAgAGYAZQByAG0AZQBuAHQAYQB0AGkAbwBuACAAaQBuACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwBlAG4AdABlAHIAaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAZQBuAHQAZQByAGkAYwB9AD0AXABcAHMAdQBtAFwAXABuAG8AbABpAG0AaQB0AHMAXwBqACgAKABOAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAPQAxACwAMgAsADQAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADEALAAyACwANAB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAARABfAHsAagA9ADMALAA1AH0AKQArACgATgBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAE0AUABXAF8AewBFAE4AVABFAFIASQBDACwAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGUAbgB0AGUAcgBpAGMAfQA9AFwAXABzAHUAbQBcAFwAbgBvAGwAaQBtAGkAdABzAF8AagAoACgATgBfAHsAagA9ADEALAAyACwANAB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAD0AMQAsADIALAA0AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAxACwAMgAsADQAfQApACsAKABOAF8AewBqAD0AMwAsADUAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagA9ADMALAA1AH0AXABcAHQAaQBtAGUAcwAgAEQAXwB7AGoAPQAzACwANQB9ACkAKwAoAE4AXwB7AGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABNAFAAVwBfAHsARQBOAFQARQBSAEkAQwAsAGoAPQAzACwANQB9AFwAXAB0AGkAbQBlAHMAIABEAFAAVwBfAHsAagA9ADMALAA1AH0AKQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqADEAMgA0AFwAIgAsACAAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABpAG4AIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANABcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAMQAyADQAXAAiACwAIABcACIAZABhAGkAbAB5ACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABjAGwAYQBzAHMAZQBzACAAagA9ADEALAAyACwANABcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABfAGoAMQAyADQAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAxACwAMgAsADQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AXwBqADMANQBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAaQBuACAAYwBsAGEAcwBzAGUAcwAgAGoAPQAzACwANQBcACIALAAgAFwAIgBoAGUAYQBkAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAMwA1AFwAIgAsACAAXAAiAGQAYQBpAGwAeQAgAGUAbgB0AGUAcgBpAGMAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAdwBlAGEAbgBlAGQAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1AFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADMALgAxAC4AMQAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAF8AagAzADUAXAAiACwAIABcACIAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AbgAgAHQAaABlACAAZgBhAHIAbQAgAGYAbwByACAAdwBlAGEAbgBlAGQAIABjAGwAYQBzAHMAZQBzACAAagA9ADMALAA1AFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAFAAVwBfAGoAMwA1AFwAIgAsACAAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAG4AIAB0AGgAZQAgAGYAYQByAG0AIABmAG8AcgAgAHAAcgBlAC0AdwBlAGEAbgBlAGQAIABoAGUAaQBmAGUAcgAgAGEAbgBkACAAYgB1AGwAbAAgAGMAYQBsAHYAZQBzAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVwBfAEUATgBUAEUAUgBJAEMAXwBqADMANQBcACIALAAgAFwAIgBkAGEAaQBsAHkAIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGgAZQBpAGYAZQByACAAYQBuAGQAIABiAHUAbABsACAAYwBhAGwAdgBlAHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgBcAG4AXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcARABQAFcAXAB1ADAAMAAyADcAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAGEAIABzAGUAcABhAHIAYQB0AGUAIABoAGEAbgBkAGwAaQBuAGcAIABvAGYAIABwAHIAZQAtAHcAZQBhAG4AZQBkACAAZAB1AHIAYQB0AGkAbwBuAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBEAGEAaQBsAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAZQBuAHQAZQByAGkAYwAgAG0AZQB0AGgAYQBuAGUAXABuAE0AXwBqAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAGoAPQAyADAALgA3AFwAXAB0AGkAbQBlAHMAIABJAF8AagBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcAG4ASQBfAGoAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQAgACgAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABJAF8AagAsAFwAbgAgACAAIAAgADIAMAAuADcAIAAqACAASQBfAGoAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABlAG4AdABlAHIAaQBjACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGgAYQByAG0AbABlAHkAIABlAHQAIABhAGwALgAgACgAMgAwADEANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAPQAyADAALgA3AFwAXAB0AGkAbQBlAHMAIABJAF8AagBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAF8AagBcACIALAAgAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBcAG4ARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAbgBJAF8AagBcAG4AawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBJAF8AagA9ACgAMQAuADEAOAA1ACsAMAAuADAAMAA0ADUANABcAFwAdABpAG0AZQBzACAAVwBfAGoALQAwAC4AMAAwADAAMAAwADIANgBcAFwAdABpAG0AZQBzACAAVwBfAGoAXgAyACsAMAAuADMAMQA1AFwAXAB0AGkAbQBlAHMAIABMAFcARwBfAGoAKQBeADIAXABcAHQAaQBtAGUAcwAgAE0AUgBfAGoAKwBNAEkAXwBqAFwAbgBXAF8AagAgAD0AIABsAGkAdgBlAHcAZQBpAGcAaAB0ACAAKABrAGcAKQBcAG4ATABXAEcAXwBqACAAPQAgAGwAaQB2AGUAdwBlAGkAZwBoAHQAIABnAGEAaQBuACAAKABrAGcALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ATQBSAF8AagAgAD0AIABpAG4AYwByAGUAYQBzAGUAIABpAG4AIABtAGUAdABhAGIAbwBsAGkAYwAgAHIAYQB0AGUAIAB3AGgAZQBuACAAcAByAG8AZAB1AGMAaQBuAGcAIABtAGkAbABrACAAKABmAHIAYQBjAHQAaQBvAG4AKQBcAG4ATQBJAF8AagAgAD0AIABhAGQAZABpAHQAaQBvAG4AYQBsACAAaQBuAHQAYQBrAGUAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABXAF8AagAsACAATABXAEcAXwBqACwAIABNAFIAXwBqACwAIABNAEkAXwBqACwAXABuACAAIAAgACAAKAAxAC4AMQA4ADUAIAArACAAMAAuADAAMAA0ADUANAAgACoAIABXAF8AagAgAC0AIAAwAC4AMAAwADAAMAAwADIANgAgACoAIABXAF8AagAgAF4AIAAyACAAKwAgADAALgAzADEANQAgACoAIABMAFcARwBfAGoAKQAgAF4AIAAyACAAKgAgAE0AUgBfAGoAIAArACAATQBJAF8AagBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkACAAaQBuAHQAYQBrAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADMALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAF8AagA9ACgAMQAuADEAOAA1ACsAMAAuADAAMAA0ADUANABcAFwAdABpAG0AZQBzACAAVwBfAGoALQAwAC4AMAAwADAAMAAwADIANgBcAFwAdABpAG0AZQBzACAAVwBfAGoAXgAyACsAMAAuADMAMQA1AFwAXAB0AGkAbQBlAHMAIABMAFcARwBfAGoAKQBeADIAXABcAHQAaQBtAGUAcwAgAE0AUgBfAGoAKwBNAEkAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAF8AagBcACIALAAgAFwAIgBsAGkAdgBlAHcAZQBpAGcAaAB0AFwAIgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAVwBHAF8AagBcACIALAAgAFwAIgBsAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgBcACIALAAgAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFIAXwBqAFwAIgAsACAAXAAiAGkAbgBjAHIAZQBhAHMAZQAgAGkAbgAgAG0AZQB0AGEAYgBvAGwAaQBjACAAcgBhAHQAZQAgAHcAaABlAG4AIABwAHIAbwBkAHUAYwBpAG4AZwAgAG0AaQBsAGsAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBJAF8AagBcACIALAAgAFwAIgBhAGQAZABpAHQAaQBvAG4AYQBsACAAaQBuAHQAYQBrAGUAIAByAGUAcQB1AGkAcgBlAGQAIABmAG8AcgAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAEEAZABkAGkAdABpAG8AbgBhAGwAIABpAG4AdABhAGsAZQAgAHIAZQBxAHUAaQByAGUAZAAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAE0ASQBfAGoAXABuAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBJAF8AagA9ACgATQBQAF8AagBcAFwAdABpAG0AZQBzACAAMQAuADAAMwBcAFwAdABpAG0AZQBzACAATgBFACkALwAoAEcARQBDAFwAXAB0AGkAbQBlAHMAIABrAFwAXAB0AGkAbQBlAHMAIABxAG0AXwBqACkAXABuAE0AUABfAGoAIAA9ACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAEwALwBoAGUAYQBkAC8AZABhAHkAKQBcAG4ATgBFACAAPQAgAG4AZQB0ACAAZQBuAGUAcgBnAHkAIAAoAE0ASgAgAG4AZQB0ACAAZQBuAGUAcgBnAHkALwBrAGcAIABtAGkAbABrACkAXABuAEcARQBDACAAPQAgAGcAcgBvAHMAcwAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgACgATQBKAC8AawBnAEQATQApAFwAbgBrACAAPQAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAIABvAGYAIABtAGUAdABhAGIAbwBsAGkAegBhAGIAbABlACAAZQBuAGUAcgBnAHkAIAB1AHMAZQAgAGYAbwByACAAbQBpAGwAawAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIAAoAGYAcgBhAGMAdABpAG8AbgApAFwAbgBxAG0AXwBqACAAPQAgAG0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkAIABvAGYAIAB0AGgAZQAgAGQAaQBlAHQAIAAoAGYAcgBhAGMAdABpAG8AbgApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAFAAXwBqACwAIABOAEUALAAgAEcARQBDACwAIABrACwAIABxAG0AXwBqACwAXABuACAAIAAgACAAKABNAFAAXwBqACAAKgAgADEALgAwADMAIAAqACAATgBFACkAIAAvACAAKABHAEUAQwAgACoAIABrACAAKgAgAHEAbQBfAGoAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAaQB0AGkAbwBuAGEAbAAgAGkAbgB0AGEAawBlACAAcgBlAHEAdQBpAHIAZQBkACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAEkAXwBqAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAEkAXwBqAD0AXABcAGYAcgBhAGMAewBNAFAAXwBqAFwAXAB0AGkAbQBlAHMAIAAxAC4AMAAzAFwAXAB0AGkAbQBlAHMAIABOAEUAfQB7AEcARQBDAFwAXAB0AGkAbQBlAHMAIABrAFwAXAB0AGkAbQBlAHMAIABxAG0AXwBqAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAVQBcACIALAAgAFwAIgBpAG4AcAB1AHQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFAAXwBqAFwAIgAsACAAXAAiAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAKABpAGYAIABpAG4AcAB1AHQAIABhAHMAIABsAGkAdAByAGUAcwAgAG8AZgAgAG0AaQBsAGsAKQBcACIALAAgAFwAIgBMAC8AaABlAGEAZAAvAGQAYQB5AFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBQAF8AagBcACIALAAgAFwAIgBtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAaQBmACAAaQBuAHAAdQB0ACAAYQBzACAAbQBpAGwAawAgAHMAbwBsAGkAZABzACkAXAAiACwAIABcACIATAAvAGgAZQBhAGQALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADMALgAzAC4AMQAuADEAIAAoADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBFAFwAIgAsACAAXAAiAG4AZQB0ACAAZQBuAGUAcgBnAHkAXAAiACwAIABcACIATQBKACAAbgBlAHQAIABlAG4AZQByAGcAeQAvAGsAZwAgAG0AaQBsAGsAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEUAQwBcACIALAAgAFwAIgBnAHIAbwBzAHMAIABlAG4AZQByAGcAeQAgAGMAbwBuAHQAZQBuAHQAXAAiACwAIABcACIATQBKAC8AawBnAEQATQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGsAXAAiACwAIABcACIAZQBmAGYAaQBjAGkAZQBuAGMAeQAgAG8AZgAgAG0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUAIABlAG4AZQByAGcAeQAgAHUAcwBlACAAZgBvAHIAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAG0AXwBqAFwAIgAsACAAXAAiAG0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkAIABvAGYAIAB0AGgAZQAgAGQAaQBlAHQAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAMwAuADMALgAxAC4AMQAgACgANgApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABtAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHUAbgBpAHQAIAB2AGEAcgBpAGEAYgBsAGUAIAB0AG8AIABhAGwAbABvAHcAIABmAG8AcgAgAHUAcwBlACAAbwBmACAAZQBpAHQAaABlAHIAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAIABvAHIAIABsAGkAdAByAGUAcwAgAG8AZgAgAG0AaQBsAGsALgBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAFwAbgBNAGkAbABrACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGMAbwBuAHYAZQByAHQAZQBkACAAZgByAG8AbQAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwBcAG4ATQBQAF8AagBcAG4ATAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBQAF8AagA9AE0AUwBfAGoALwAoADAALgAwADEAXABcAHQAaQBtAGUAcwAgACgARgBDAF8AagArAFAAQwBfAGoAKQApAFwAbgBNAFMAXwBqACAAPQAgAGQAYQBpAGwAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGkAbABrACAAcwBvAGwAaQBkAHMAIAAoAGsAZwAgAE0AUwAvAGgAZQBhAGQALwBkAGEAeQApAFwAbgBGAEMAXwBqACAAPQAgAGYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4AUABDAF8AagAgAD0AIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAFMAXwBqACwAIABGAEMAXwBqACwAIABQAEMAXwBqACwAXABuACAAIAAgACAATQBTAF8AagAgAC8AIAAoADAALgAwADEAIAAqACAAKABGAEMAXwBqACAAKwAgAFAAQwBfAGoAKQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAYwBvAG4AdgBlAHIAdABlAGQAIABmAHIAbwBtACAAbQBpAGwAawAgAHMAbwBsAGkAZABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBQAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBQAF8AagA9AFwAXABmAHIAYQBjAHsATQBTAF8AagB9AHsAMAAuADAAMQBcAFwAdABpAG0AZQBzACAAKABGAEMAXwBqACsAUABDAF8AagApAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUABVAFwAIgAsACAAXAAiAGkAbgBwAHUAdAAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAdQBuAGkAdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUwBfAGoAXAAiACwAIABcACIAZABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwBcACIALAAgAFwAIgBrAGcAIABNAFMALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEMAXwBqAFwAIgAsACAAXAAiAGYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAQwBfAGoAXAAiACwAIABcACIAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUABVAFwAIgAsACAAXAAiAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAdQBuAGkAdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AUwBfAGoAXAAiACwAIABcACIAZABhAGkAbAB5ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwBcACIALAAgAFwAIgBrAGcAIABNAFMALwBoAGUAYQBkAC8AZABhAHkAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEMAXwBqAFwAIgAsACAAXAAiAGYAYQB0ACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAGYAYQB0ACAAYQBuAGQAIABwAHIAbwB0AGUAaQBuACAAYwBvAHIAcgBlAGMAdABlAGQAIABtAGkAbABrAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAQwBfAGoAXAAiACwAIABcACIAcAByAG8AdABlAGkAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIABmAGEAdAAgAGEAbgBkACAAcAByAG8AdABlAGkAbgAgAGMAbwByAHIAZQBjAHQAZQBkACAAbQBpAGwAawBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAdQBuAGkAdAAgAHYAYQByAGkAYQBiAGwAZQAgAHQAbwAgAGEAbABsAG8AdwAgAGYAbwByACAAdQBzAGUAIABvAGYAIABlAGkAdABoAGUAcgAgAG0AaQBsAGsAIABzAG8AbABpAGQAcwAgAG8AcgAgAGwAaQB0AHIAZQBzACAAbwBmACAAbQBpAGwAawAuACAAQwBvAG4AdgBlAHIAdABlAGQAIABpAG4AcAB1AHQAIABGAEMAIABhAG4AZAAgAFAAQwAgAHAAZQByAGMAZQBuAHQAIAB0AG8AIABpAG4AdABlAGcAZQByAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABcAG4ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQAgAG8AZgAgAGQAaQBlAHQAXABuAHEAbQBfAGoAXABuAGYAcgBhAGMAdABpAG8AbgBcAG4AcQBtAF8AagA9ADAALgA3ADkANQBcAFwAdABpAG0AZQBzACAAKABEAE0ARABfAGoAXABcAHQAaQBtAGUAcwAgADEAMAAwACkALQAwAC4AMAAwADEANABcAG4ARABNAEQAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAZQB4AHAAcgBlAHMAcwBlAGQAIABhAHMAIABhACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQATQBEAF8AagAsAFwAbgAgACAAIAAgADAALgA3ADkANQAgACoAIAAoAEQATQBEAF8AagAgACoAIAAxADAAMAApACAALQAgADAALgAwADAAMQA0AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABNAEQAXwBqACwAXABuACAAIAAgACAAMAAuADAAMAA3ADkANQAgACoAIAAoAEQATQBEAF8AagAgACoAIAAxADAAMAApACAALQAgADAALgAwADAAMQA0AFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5ACAAbwBmACAAZABpAGUAdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHEAbQBfAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAzAC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcQBtAF8AagA9ADAALgA3ADkANQBcAFwAdABpAG0AZQBzACAAKABEAE0ARABfAGoAXABcAHQAaQBtAGUAcwAgADEAMAAwACkALQAwAC4AMAAwADEANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBxAG0AXwBqAD0AMAAuADAAMAA3ADkANQBcAFwAdABpAG0AZQBzACAAKABEAE0ARABfAGoAXABcAHQAaQBtAGUAcwAgADEAMAAwACkALQAwAC4AMAAwADEANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABNAEQAXwBqAFwAIgAsACAAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAZQB4AHAAcgBlAHMAcwBlAGQAIABhAHMAIABhACAAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABjAGgAYQBuAGcAZQBkACAAMAAuADcAOQA1ACAAdABvACAAMAAuADAAMAA3ADkANQAgAHcAaABpAGMAaAAgAGkAcwAgAHQAaABlACAAdgBhAGwAdQBlACAAdQBzAGUAZAAgAGkAbgAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdABcACIAKQA7AFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAXwBEAGEAaQByAHkAIgAsACIAdABlAHgAdAAiADoAIgBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4ASQBuAE0ATQBTAEEAZgB0AGUAcgBTAG8AbABpAGQAUwBlAHAAYQByAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAE0ATQBTAEYAcgBhAGMAdABpAG8AbgAsACAARgByAGEAYwB0AGkAbwBuAFMAZQBwAGEAcgBhAHQAZQBkACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAgACoAIAAoAE0ATQBTAEYAcgBhAGMAdABpAG8AbgAtACgATQBNAFMARgByAGEAYwB0AGkAbwBuACoARgByAGEAYwB0AGkAbwBuAFMAZQBwAGEAcgBhAHQAZQBkACkAKQBcAG4AKQA7AFwAbgBcAG4AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAEkAbgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAbgBpAHQAYQBsAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAEYAcgBhAGMAdABpAG8AbgAsAFwAbgAgACAAIAAgAE0ATQBTADEARgByAGEAYwB0AGkAbwBuACwAIABNAE0AUwAxAFMAZQBwAGEAcgBhAHQAZQBkACwAIABcAG4AIAAgACAAIABNAE0AUwAyAEYAcgBhAGMAdABpAG8AbgAsACAATQBNAFMAMgBTAGUAcABhAHIAYQB0AGUAZAAsACAAXABuACAAIAAgACAATQBNAFMAMwBGAHIAYQBjAHQAaQBvAG4ALAAgAE0ATQBTADMAUwBlAHAAYQByAGEAdABlAGQALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACAAKgAgACgAXABuACAAIAAgACAAIAAgACAAIABJAG4AaQB0AGEAbABTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBGAHIAYQBjAHQAaQBvAG4AIAArAFwAbgAgACAAIAAgACAAIAAgACAAKABNAE0AUwAxAEYAcgBhAGMAdABpAG8AbgAgACoAIABNAE0AUwAxAFMAZQBwAGEAcgBhAHQAZQBkACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAKABNAE0AUwAyAEYAcgBhAGMAdABpAG8AbgAgACoAIABNAE0AUwAyAFMAZQBwAGEAcgBhAHQAZQBkACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAKABNAE0AUwAzAEYAcgBhAGMAdABpAG8AbgAgACoAIABNAE0AUwAzAFMAZQBwAGEAcgBhAHQAZQBkACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVgBhAGkAcgBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQgBlAGUAZgBDAGEAdAB0AGwAZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBCAGUAZQBmAEMAYQB0AHQAbABlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AQwBoAGkAYwBrAGUAbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEMAaABpAGMAawBlAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBDAGgAaQBjAGsAZQBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBEAGEAaQByAHkAYwBhAHQAdABsAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8ARABhAGkAcgB5AGMAYQB0AHQAbABlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAEQAYQBpAHIAeQBjAGEAdAB0AGwAZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBWAGEAaQByAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBQAGkAZwBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFAAaQBnAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAFAAcgBvAGQAdQBjAHQAXwBTAGgAZQBlAHAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBQAHIAbwBkAHUAYwB0AF8AUwBoAGUAZQBwAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUAByAG8AZAB1AGMAdABfAFMAaABlAGUAcABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUASABhAHIAdgBlAHMAdABJAG4AZABlAHgAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQwBvAHcAcwBBAG4AZABIAGUAaQBmAGUAcgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEMAbwB3AHMAQQBuAGQASABlAGkAZgBlAHIAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABDAG8AdwBzAEEAbgBkAEgAZQBpAGYAZQByAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQgB1AGwAbABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEIAdQBsAGwAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABCAHUAbABsAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AQwBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBDAEYAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAEEAbgBkAEYAcgBhAGMARwBBAFMATQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAQQBuAGQARgByAGEAYwBHAEEAUwBNAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBBAG4AZABGAHIAYQBjAEcAQQBTAE0AXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAHIAZQBXAGUAYQBuAGUAZABDAGEAbAB2AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAcgBlAFcAZQBhAG4AZQBkAEMAYQBsAHYAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUAByAGUAVwBlAGEAbgBlAGQAQwBhAGwAdgBlAHMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEkAbgBjAHIAZQBhAHMAZQBkAE0AZQB0AGEAYgBvAGwAaQBjAFIAYQB0AGUATQBpAGwAawBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ASQBuAGMAcgBlAGEAcwBlAGQATQBlAHQAYQBiAG8AbABpAGMAUgBhAHQAZQBNAGkAbABrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBJAG4AYwByAGUAYQBzAGUAZABNAGUAdABhAGIAbwBsAGkAYwBSAGEAdABlAE0AaQBsAGsAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBWAG8AaQBkAGUAZABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFYAbwBpAGQAZQBkAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVgBvAGkAZABlAGQATQBNAFMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUARgBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBQAGUAcgBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBGAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAFAAZQByAE0ATQBTAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAEYATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUAUABlAHIATQBNAFMAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE4AZQB0AEUAbgBlAHIAZwB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBOAGUAdABFAG4AZQByAGcAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATgBlAHQARQBuAGUAcgBnAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEcAcgBvAHMAcwBFAG4AZQByAGcAeQBDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBHAHIAbwBzAHMARQBuAGUAcgBnAHkAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARwByAG8AcwBzAEUAbgBlAHIAZwB5AEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAZgBmAGkAYwBpAGUAbgBjAHkATwBmAFUAcwBlAE8AZgBNAGUAdABhAGIAbwBsAGkAegBhAGIAbABlAEUAbgBlAHIAZwB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAGYAZgBpAGMAaQBlAG4AYwB5AE8AZgBVAHMAZQBPAGYATQBlAHQAYQBiAG8AbABpAHoAYQBiAGwAZQBFAG4AZQByAGcAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBmAGYAaQBjAGkAZQBuAGMAeQBPAGYAVQBzAGUATwBmAE0AZQB0AGEAYgBvAGwAaQB6AGEAYgBsAGUARQBuAGUAcgBnAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwB0AGkAbwBuAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAHQAaQBvAG4ATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMAdABpAG8AbgBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAcgBhAGMARwBBAFMATQBTAG8AaQBsAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAHIAYQBjAEcAQQBTAE0AUwBvAGkAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgByAGEAYwBHAEEAUwBNAFMAbwBpAGwAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8ARgBhAHQAQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBGAGEAdABDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEYAYQB0AEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABJAG4ATQBpAGwAawBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AEkAbgBNAGkAbABrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQASQBuAE0AaQBsAGsAXwBEAGEAdABhACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEYAcgBvAG0ARQBuAHQAZQByAGkAYwBGAGUAcgBtAGUAbgB0AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARgByAG8AbQBFAG4AdABlAHIAaQBjAEYAZQByAG0AZQBuAHQAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBGAHIAbwBtAEUAbgB0AGUAcgBpAGMARgBlAHIAbQBlAG4AdABhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADIAXwBEAGEAaQBsAHkARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMgBfAEQAYQBpAGwAeQBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAyAF8ARABhAGkAbAB5AEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwAzAF8ARAByAHkATQBhAHQAdABlAHIARgBlAGUAZABJAG4AdABhAGsAZQBfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8AMwBfAEQAcgB5AE0AYQB0AHQAZQByAEYAZQBlAGQASQBuAHQAYQBrAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADMAXwBEAHIAeQBNAGEAdAB0AGUAcgBGAGUAZQBkAEkAbgB0AGEAawBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANABfAEEAZABkAGkAdABpAG8AbgBhAGwASQBuAHQAYQBrAGUARgBvAHIATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA0AF8AQQBkAGQAaQB0AGkAbwBuAGEAbABJAG4AdABhAGsAZQBGAG8AcgBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADQAXwBBAGQAZABpAHQAaQBvAG4AYQBsAEkAbgB0AGEAawBlAEYAbwByAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBVAG4AaQB0ACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADUAXwBNAGkAbABrAFAAcgBvAGQAdQBjAHQAaQBvAG4ARgByAG8AbQBNAGkAbABrAFMAbwBsAGkAZABzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANQBfAE0AaQBsAGsAUAByAG8AZAB1AGMAdABpAG8AbgBGAHIAbwBtAE0AaQBsAGsAUwBvAGwAaQBkAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBfAE0AZQB0AGgAbwBkADIAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA1AF8ATQBpAGwAawBQAHIAbwBkAHUAYwB0AGkAbwBuAEYAcgBvAG0ATQBpAGwAawBTAG8AbABpAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AVABpAHQAbABlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFUAbgBpAHQAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFMAbwB1AHIAYwBlACIALAAiAEUAbgB0AGUAcgBpAGMATQBlAHQAaABhAG4AZQBfAEQAYQBpAHIAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMwBfADMAXwAxAF8AMQBfAF8ANgBfAE0AZQB0AGEAYgBvAGwAaQBzAGEAYgBpAGwAaQB0AHkATwBmAEQAaQBlAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBFAG4AdABlAHIAaQBjAE0AZQB0AGgAYQBuAGUAXwBEAGEAaQByAHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADMAXwAzAF8AMQBfADEAXwBfADYAXwBNAGUAdABhAGIAbwBsAGkAcwBhAGIAaQBsAGkAdAB5AE8AZgBEAGkAZQB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBuAHQAZQByAGkAYwBNAGUAdABoAGEAbgBlAF8ARABhAGkAcgB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAzAF8AMwBfADEAXwAxAF8AXwA2AF8ATQBlAHQAYQBiAG8AbABpAHMAYQBiAGkAbABpAHQAeQBPAGYARABpAGUAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwBfAEQAYQBpAHIAeQAuAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBJAG4ATQBNAFMAQQBmAHQAZQByAFMAbwBsAGkAZABTAGUAcABhAHIAYQB0AGkAbwBuACIALAAiAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwBfAEQAYQBpAHIAeQAuAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBJAG4AUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -25956,21 +25967,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>